--- a/server/excel/release/system-text.xlsx
+++ b/server/excel/release/system-text.xlsx
@@ -695,7 +695,7 @@
     <t xml:space="preserve">Nện trứng vàng</t>
   </si>
   <si>
-    <t xml:space="preserve">Đại hiệp thân mến: &lt;br&gt; Ngài có còn thừa chưa sử dụng nện trứng lượt, hiện thông qua Nguyên bảo trả về, xin chú ý kiểm tra và nhận!</t>
+    <t xml:space="preserve">Đại hiệp thân mến: &lt;br&gt; Ngài có còn thừa chưa sử dụng nện trứng lượt, hiện thông qua Kim cương trả về, xin chú ý kiểm tra và nhận!</t>
   </si>
   <si>
     <t xml:space="preserve">Nguyên Tiêu hỉ nhạc</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">Đại hiệp thân mến: &lt;br&gt; Chúc mừng ngài tại lần này &lt;2403 Nguyên Tiêu hỉ nhạc &gt; Bài thi bảng xếp hạng bên trong nhận được &lt;2464 {d}&gt; Thứ tự, có thể đạt được trở xuống thưởng!</t>
   </si>
   <si>
-    <t xml:space="preserve">Vượt phục Nguyên bảo tiêu hao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đại hiệp thân mến: &lt;br&gt; Chúc mừng ngài tại lần này &lt;2403 Vượt phục Nguyên bảo tiêu hao &gt; Bảng xếp hạng bên trong nhận được &lt;2464 {d}&gt; Thứ tự, có thể đạt được trở xuống thưởng!</t>
+    <t xml:space="preserve">Vượt phục Kim cương tiêu hao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đại hiệp thân mến: &lt;br&gt; Chúc mừng ngài tại lần này &lt;2403 Vượt phục Kim cương tiêu hao &gt; Bảng xếp hạng bên trong nhận được &lt;2464 {d}&gt; Thứ tự, có thể đạt được trở xuống thưởng!</t>
   </si>
   <si>
     <t xml:space="preserve">Nạp tiền xếp hạng</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">Tân phục trở lại lợi</t>
   </si>
   <si>
-    <t xml:space="preserve">Đại hiệp thân mến đại nhân: Cảm tạ ngài tham dự tân phục trở lại lợi hoạt động, trở xuống là ngài tổng cộng nhận được hoạt động Nguyên bảo</t>
+    <t xml:space="preserve">Đại hiệp thân mến đại nhân: Cảm tạ ngài tham dự tân phục trở lại lợi hoạt động, trở xuống là ngài tổng cộng nhận được hoạt động Kim cương</t>
   </si>
   <si>
     <t xml:space="preserve">Phạm Đức tát phát dùng tay phiệt yêu sắc thả</t>
@@ -1376,16 +1376,16 @@
     <t xml:space="preserve">tiền xu hiến cho</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;2420 {s}&gt; Tiến hành Nguyên bảo hiến cho.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nguyên bảo hiến cho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;2420 {s}&gt; Tiến hành chí tôn Nguyên bảo hiến cho.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí tôn Nguyên bảo hiến cho</t>
+    <t xml:space="preserve">&lt;2420 {s}&gt; Tiến hành Kim cương hiến cho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kim cương hiến cho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;2420 {s}&gt; Tiến hành chí tôn Kim cương hiến cho.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chí tôn Kim cương hiến cho</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;2420 {s}&gt; Công kích thứ &lt;2405 {d}&gt; Chương Bang BOSS&lt;2405 {d}&gt; Lần, chung tạo thành &lt;2405 {d}&gt; Tổn thương.</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">Pháp bảo</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mỗi cái phó bản mỗi ngày có 2 Lần miễn phí khiêu chiến lượt &lt;br&gt;2. Tăng lên vip Cấp có thể hối đoái ngoài định mức thu hoạch lượt &lt;br&gt;3. Mỗi quan lần thứ nhất khiêu chiến miễn phí lại không khấu trừ khiêu chiến lượt &lt;br&gt;4. Một khóa càn quét có thể chia làm hai loại: Miễn phí càn quét, Nguyên bảo càn quét. Người chơi nhưng căn cứ từ mình nhu cầu lựa chọn càn quét loại hình.</t>
+    <t xml:space="preserve">1. Mỗi cái phó bản mỗi ngày có 2 Lần miễn phí khiêu chiến lượt &lt;br&gt;2. Tăng lên vip Cấp có thể hối đoái ngoài định mức thu hoạch lượt &lt;br&gt;3. Mỗi quan lần thứ nhất khiêu chiến miễn phí lại không khấu trừ khiêu chiến lượt &lt;br&gt;4. Một khóa càn quét có thể chia làm hai loại: Miễn phí càn quét, Kim cương càn quét. Người chơi nhưng căn cứ từ mình nhu cầu lựa chọn càn quét loại hình.</t>
   </si>
   <si>
     <t xml:space="preserve">Mỗi ngày phó bản</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">Côn Luân bí cảnh</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Chiến sĩ, pháp sư, xe tăng, phụ trợ  4 Cái nghề nghiệp đối ứng riêng phần mình tiên minh kỹ năng, mỗi một loại chỉ đối ứng nghề nghiệp tăng thêm &lt;br&gt;2. Người chơi đem nghề nghiệp bên trong mỗi cái theo trình tự kỹ năng kích hoạt, mở ra tiếp theo giai đoạn kỹ năng theo trình tự &lt;br&gt;3. Người chơi rời khỏi hoặc bị gỡ ra tiên minh sau, tiên minh kỹ năng sẽ tiếp tục có hiệu lực; Lần sau lại thêm vào cái khác tiên minh lúc, đã thăng cấp kỹ năng sẽ bị kế thừa đến mới tiên minh &lt;br&gt;4. Nhưng thiết lập lại chỉ định tiên minh kỹ năng, thiết lập lại sau nghề nghiệp đấy kỹ năng cấp thanh không, đồng thời trở về tiêu hao  50% Kim tệ  Cùng  100% Tiên minh kinh nghiệm . Kỹ năng tổng cấp càng cao thiết lập lại tiêu hao  Nguyên bảo  Càng cao, lần đầu thiết lập lại chỉ cần tiêu hao  300 Nguyên bảo &lt;br&gt;5. Tiên minh thông thường kỹ năng cấp max cấp sau nhưng mở ra đối ứng nghề nghiệp  Tiên minh PVP Thuộc tính cùng kỹ năng .Tiên minh PVP Thuộc tính  Tăng lên tới chỉ định cấp, sắp mở ra đối ứng  Tiên minh PVP Kỹ năng &lt;br&gt;6. Tiên minh PVP Thuộc tính thiết lập lại sau, bổn hệ PVP Kỹ năng đem bị phong ấn, kỹ năng cấp đem bị giữ lại nhưng không còn có hiệu lực. Đồng thời  100% Trả về tiêu hao dưỡng thành vật liệu.PVP Thuộc tính cấp càng cao, thiết lập lại tiêu hao Nguyên bảo càng cao, lần đầu thiết lập lại chỉ cần tiêu hao  300 Nguyên bảo &lt;br&gt;7. Tiên minh PVP Kỹ năng cấp tăng lên thụ bản chức nghiệp PVP Thuộc tính cấp ảnh hưởng.&lt;br&gt;8. Tiên minh PVP Kỹ năng lãng quên sau, đối ứng PVP Kỹ năng cấp thiết lập lại vì 1 Cấp, đồng thời  100% Trả về tiêu hao dưỡng thành vật liệu.</t>
+    <t xml:space="preserve">1. Chiến sĩ, pháp sư, xe tăng, phụ trợ  4 Cái nghề nghiệp đối ứng riêng phần mình tiên minh kỹ năng, mỗi một loại chỉ đối ứng nghề nghiệp tăng thêm &lt;br&gt;2. Người chơi đem nghề nghiệp bên trong mỗi cái theo trình tự kỹ năng kích hoạt, mở ra tiếp theo giai đoạn kỹ năng theo trình tự &lt;br&gt;3. Người chơi rời khỏi hoặc bị gỡ ra tiên minh sau, tiên minh kỹ năng sẽ tiếp tục có hiệu lực; Lần sau lại thêm vào cái khác tiên minh lúc, đã thăng cấp kỹ năng sẽ bị kế thừa đến mới tiên minh &lt;br&gt;4. Nhưng thiết lập lại chỉ định tiên minh kỹ năng, thiết lập lại sau nghề nghiệp đấy kỹ năng cấp thanh không, đồng thời trở về tiêu hao  50% Kim tệ  Cùng  100% Tiên minh kinh nghiệm . Kỹ năng tổng cấp càng cao thiết lập lại tiêu hao  Kim cương  Càng cao, lần đầu thiết lập lại chỉ cần tiêu hao  300 Kim cương &lt;br&gt;5. Tiên minh thông thường kỹ năng cấp max cấp sau nhưng mở ra đối ứng nghề nghiệp  Tiên minh PVP Thuộc tính cùng kỹ năng .Tiên minh PVP Thuộc tính  Tăng lên tới chỉ định cấp, sắp mở ra đối ứng  Tiên minh PVP Kỹ năng &lt;br&gt;6. Tiên minh PVP Thuộc tính thiết lập lại sau, bổn hệ PVP Kỹ năng đem bị phong ấn, kỹ năng cấp đem bị giữ lại nhưng không còn có hiệu lực. Đồng thời  100% Trả về tiêu hao dưỡng thành vật liệu.PVP Thuộc tính cấp càng cao, thiết lập lại tiêu hao Kim cương càng cao, lần đầu thiết lập lại chỉ cần tiêu hao  300 Kim cương &lt;br&gt;7. Tiên minh PVP Kỹ năng cấp tăng lên thụ bản chức nghiệp PVP Thuộc tính cấp ảnh hưởng.&lt;br&gt;8. Tiên minh PVP Kỹ năng lãng quên sau, đối ứng PVP Kỹ năng cấp thiết lập lại vì 1 Cấp, đồng thời  100% Trả về tiêu hao dưỡng thành vật liệu.</t>
   </si>
   <si>
     <t xml:space="preserve">Tiên minh kỹ năng</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mỗi lần khiêu chiến phó bản bên trong Boss Đều sẽ đạt được  Tiên minh cống hiến ,  Kim tệ &lt;br&gt;2. Đánh giết Boss Sau căn cứ tiên minh thành viên đối bản Boss Tạo thành tổn thương xếp hạng cấp cho kết toán thưởng, đánh giết người nhưng ngoài định mức nhận được đánh giết thưởng, đồng thời tiên minh có thể đạt được nhất định  Tiên minh kinh nghiệm &lt;br&gt;3. Người chơi mỗi ngày có được  2 Lần miễn phí khiêu chiến lượt, lượt tại mỗi ngày  00:00 Thiết lập lại, ngoài ra người chơi nhưng tiêu hao  Nguyên bảo  Hối đoái ngoài định mức khiêu chiến lượt &lt;br&gt;4. Càn quét sẽ kế thừa lần trước khiêu chiến tổn thương lượng tiến hành kết toán, càn quét đồng dạng tiêu hao  1 Điểm khiêu chiến lượt &lt;br&gt;5. Tiêu hao  Nguyên bảo  Nhưng kích hoạt hoặc tăng lên tiên minh toàn viên gia tăng công kích Buff Hiệu quả, lớn nhất có thể gia tăng đến  20% Lực công kích tăng thêm. Mỗi cái Boss Đánh giết thưởng mỗi cái nhân vật có thể đạt được  1 Lần, thay đổi tiên minh lặp lại đánh giết BOSS Chỉ có thể nhận được tổn thương thưởng cùng đánh giết thưởng, không thể lặp lại nhận được bảng xếp hạng thưởng.&lt;br&gt;6. Tiên minh BOSS Ích lợi người chơi chỉ có thể thu hoạch 1 Lần, người chơi lần nữa tiến vào mới tiên minh, như mới tiên minh BOSS Tiến độ nhỏ hơn lão tiên minh BOSS Tiến độ, thì người chơi không cách nào nhận được ích lợi, thẳng đến mới tiên minh BOSS Tiến độ đuổi kịp lão tiên minh, người chơi mới có thể tiếp tục nhận được ích lợi.</t>
+    <t xml:space="preserve">1. Mỗi lần khiêu chiến phó bản bên trong Boss Đều sẽ đạt được  Tiên minh cống hiến ,  Kim tệ &lt;br&gt;2. Đánh giết Boss Sau căn cứ tiên minh thành viên đối bản Boss Tạo thành tổn thương xếp hạng cấp cho kết toán thưởng, đánh giết người nhưng ngoài định mức nhận được đánh giết thưởng, đồng thời tiên minh có thể đạt được nhất định  Tiên minh kinh nghiệm &lt;br&gt;3. Người chơi mỗi ngày có được  2 Lần miễn phí khiêu chiến lượt, lượt tại mỗi ngày  00:00 Thiết lập lại, ngoài ra người chơi nhưng tiêu hao  Kim cương  Hối đoái ngoài định mức khiêu chiến lượt &lt;br&gt;4. Càn quét sẽ kế thừa lần trước khiêu chiến tổn thương lượng tiến hành kết toán, càn quét đồng dạng tiêu hao  1 Điểm khiêu chiến lượt &lt;br&gt;5. Tiêu hao  Kim cương  Nhưng kích hoạt hoặc tăng lên tiên minh toàn viên gia tăng công kích Buff Hiệu quả, lớn nhất có thể gia tăng đến  20% Lực công kích tăng thêm. Mỗi cái Boss Đánh giết thưởng mỗi cái nhân vật có thể đạt được  1 Lần, thay đổi tiên minh lặp lại đánh giết BOSS Chỉ có thể nhận được tổn thương thưởng cùng đánh giết thưởng, không thể lặp lại nhận được bảng xếp hạng thưởng.&lt;br&gt;6. Tiên minh BOSS Ích lợi người chơi chỉ có thể thu hoạch 1 Lần, người chơi lần nữa tiến vào mới tiên minh, như mới tiên minh BOSS Tiến độ nhỏ hơn lão tiên minh BOSS Tiến độ, thì người chơi không cách nào nhận được ích lợi, thẳng đến mới tiên minh BOSS Tiến độ đuổi kịp lão tiên minh, người chơi mới có thể tiếp tục nhận được ích lợi.</t>
   </si>
   <si>
     <t xml:space="preserve">Tiên minh phó bản</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">Đồ đằng Thánh Điện</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Khiêu chiến lượt vì tất cả phó bản dùng chung &lt;br&gt;2. Khiêu chiến thất bại không tiêu hao lượt &lt;br&gt;3. Khiêu chiến lượt mỗi ngày  0 Điểm đổi mới &lt;br&gt;4. Mỗi ngày nhưng tiêu hao  Nguyên bảo  Ngoài định mức hối đoái  2 Lần khiêu chiến lượt</t>
+    <t xml:space="preserve">1. Khiêu chiến lượt vì tất cả phó bản dùng chung &lt;br&gt;2. Khiêu chiến thất bại không tiêu hao lượt &lt;br&gt;3. Khiêu chiến lượt mỗi ngày  0 Điểm đổi mới &lt;br&gt;4. Mỗi ngày nhưng tiêu hao  Kim cương  Ngoài định mức hối đoái  2 Lần khiêu chiến lượt</t>
   </si>
   <si>
     <t xml:space="preserve">Đồ đằng Thánh Điện - Khiêu chiến lượt</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">Kim tệ thu hoạch</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Linh Lung Tháp thủ thông có thể đạt được  Tiến giai thạch  Thưởng, mỗi thông quan  10 Tầng nhưng ngoài định mức nhận một phần thông quan thưởng.&lt;br&gt;2. Mỗi một tầng lần đầu khiêu chiến không tiêu hao khiêu chiến lượt, đã thông quan tầng có thể tiến hành càn quét, mỗi ngày có  2 Lần miễn phí càn quét lượt.&lt;br&gt;3. Miễn phí càn quét lượt mỗi ngày  0 Điểm đổi mới.&lt;br&gt;4. Nhưng tiêu hao  Nguyên bảo  Sau mua khiêu chiến lượt, mỗi ngày hạn mua  3 Lần &lt;br&gt;5. Nội dung chính tuyến  360 Quan thông quan sau mở ra chủng tộc tháp &lt;br&gt;6. Người chơi cấp  40 Cấp  Sau mở ra tự động quét tháp công năng, tự động quét tháp số tầng tích luỹ hạn mức cao nhất vì  100 Tầng , đương quét tháp số tầng tích luỹ đến hạn mức cao nhất sau tự động kết thúc tự động quét tháp công năng.</t>
+    <t xml:space="preserve">1. Linh Lung Tháp thủ thông có thể đạt được  Tiến giai thạch  Thưởng, mỗi thông quan  10 Tầng nhưng ngoài định mức nhận một phần thông quan thưởng.&lt;br&gt;2. Mỗi một tầng lần đầu khiêu chiến không tiêu hao khiêu chiến lượt, đã thông quan tầng có thể tiến hành càn quét, mỗi ngày có  2 Lần miễn phí càn quét lượt.&lt;br&gt;3. Miễn phí càn quét lượt mỗi ngày  0 Điểm đổi mới.&lt;br&gt;4. Nhưng tiêu hao  Kim cương  Sau mua khiêu chiến lượt, mỗi ngày hạn mua  3 Lần &lt;br&gt;5. Nội dung chính tuyến  360 Quan thông quan sau mở ra chủng tộc tháp &lt;br&gt;6. Người chơi cấp  40 Cấp  Sau mở ra tự động quét tháp công năng, tự động quét tháp số tầng tích luỹ hạn mức cao nhất vì  100 Tầng , đương quét tháp số tầng tích luỹ đến hạn mức cao nhất sau tự động kết thúc tự động quét tháp công năng.</t>
   </si>
   <si>
     <t xml:space="preserve">Linh Lung Tháp</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">Tướng tin tức - Thiên phú</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Thông qua đổi mới có thể quét ra phẩm chất cao treo thưởng nhiệm vụ, nhiệm vụ phẩm chất càng cao thưởng càng phong phú.&lt;br&gt;2. Mỗi ngày có  2 Lần miễn phí đổi mới cơ hội, cũng có thể tiêu hao đổi mới quyển hoặc Nguyên bảo tiến hành đổi mới.&lt;br&gt;3. Tại điều động giao diện bên trong, phía dưới bên trái nhất đồ tiêu biểu thị tướng cần thỏa mãn  Tinh cấp  Điều kiện, còn lại là tướng cần thỏa mãn trận doanh điều kiện.&lt;br&gt;4. Đương tướng thỏa mãn chỉ định điều kiện sau, nhưng tiêu hao nhất định lệnh treo giải thưởng xác nhận đơn đặt hàng.&lt;br&gt;5. Mỗi lần xác nhận sau khi thành công, treo thưởng nhiệm vụ cần tiến hành cùng một đoạn thời gian, tại trong lúc này đã điều động tướng không cách nào chấp hành những nhiệm vụ khác.&lt;br&gt;6. Lệnh treo giải thưởng số lượng đạt tới hạn mức cao nhất sau, offline treo máy sẽ không còn nhận được lệnh treo giải thưởng, mời kịp thời sử dụng a</t>
+    <t xml:space="preserve">1. Thông qua đổi mới có thể quét ra phẩm chất cao treo thưởng nhiệm vụ, nhiệm vụ phẩm chất càng cao thưởng càng phong phú.&lt;br&gt;2. Mỗi ngày có  2 Lần miễn phí đổi mới cơ hội, cũng có thể tiêu hao đổi mới quyển hoặc Kim cương tiến hành đổi mới.&lt;br&gt;3. Tại điều động giao diện bên trong, phía dưới bên trái nhất đồ tiêu biểu thị tướng cần thỏa mãn  Tinh cấp  Điều kiện, còn lại là tướng cần thỏa mãn trận doanh điều kiện.&lt;br&gt;4. Đương tướng thỏa mãn chỉ định điều kiện sau, nhưng tiêu hao nhất định lệnh treo giải thưởng xác nhận đơn đặt hàng.&lt;br&gt;5. Mỗi lần xác nhận sau khi thành công, treo thưởng nhiệm vụ cần tiến hành cùng một đoạn thời gian, tại trong lúc này đã điều động tướng không cách nào chấp hành những nhiệm vụ khác.&lt;br&gt;6. Lệnh treo giải thưởng số lượng đạt tới hạn mức cao nhất sau, offline treo máy sẽ không còn nhận được lệnh treo giải thưởng, mời kịp thời sử dụng a</t>
   </si>
   <si>
     <t xml:space="preserve">Treo thưởng</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">Tiên minh thành viên</t>
   </si>
   <si>
-    <t xml:space="preserve">Lần đầu thiết lập lại chỉ cần  {s}Nguyên bảo , thiết lập lại sau trước mắt nghề nghiệp tất cả kỹ năng cấp đem bị thanh không ( Biến thành chưa kích hoạt trạng thái ), mời thận trọng cân nhắc!, đồng thời trở về tiêu hao  100%Tiên minh kinh nghiệm  Cùng  50% Kim tệ </t>
+    <t xml:space="preserve">Lần đầu thiết lập lại chỉ cần  {s}Kim cương , thiết lập lại sau trước mắt nghề nghiệp tất cả kỹ năng cấp đem bị thanh không ( Biến thành chưa kích hoạt trạng thái ), mời thận trọng cân nhắc!, đồng thời trở về tiêu hao  100%Tiên minh kinh nghiệm  Cùng  50% Kim tệ </t>
   </si>
   <si>
     <t xml:space="preserve">1. Người chơi có thể thông qua hết thành nhiệm vụ đến nhận được [ Cẩm nang ], góp nhặt số lượng nhất định [ Cẩm nang ] Có thể giải tỏa thưởng &lt;br&gt;2. Mỗi ngày nhiệm vụ 0 Điểm thiết lập lại</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">Cẩm nang chi mê</t>
   </si>
   <si>
-    <t xml:space="preserve">Thiết lập lại cần tiêu hao  {s}Nguyên bảo , thiết lập lại sau trước mắt nghề nghiệp tất cả kỹ năng cấp đem bị thanh không ( Biến thành chưa kích hoạt trạng thái ), đồng thời trở về tiêu hao  100%Tiên minh kinh nghiệm  Cùng  50% Kim tệ , mời thận trọng cân nhắc!</t>
+    <t xml:space="preserve">Thiết lập lại cần tiêu hao  {s}Kim cương , thiết lập lại sau trước mắt nghề nghiệp tất cả kỹ năng cấp đem bị thanh không ( Biến thành chưa kích hoạt trạng thái ), đồng thời trở về tiêu hao  100%Tiên minh kinh nghiệm  Cùng  50% Kim tệ , mời thận trọng cân nhắc!</t>
   </si>
   <si>
     <t xml:space="preserve">1. Người chơi có thể thông qua hết thành mỗi ngày nhiệm vụ, nhận được [ Công huân ] Kinh nghiệm đạo cụ, đạo cụ có thể tăng lên công lao sổ ghi chép hoạt động cấp, đồng thời có thể nhận cơ sở thưởng &lt;br&gt;2. Hoạt động kết thúc sau, tích luỹ cấp, nhiệm vụ tiến độ cùng kinh nghiệm sẽ thanh trừ, mời kịp thời hoàn thành nhiệm vụ, nhận thưởng, để tránh bỏ lỡ thưởng a &lt;br&gt;3. Mỗi ngày nhiệm vụ 0 Điểm thiết lập lại</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">Thú hồn</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mỗi lần khiêu chiến đều đem tiêu hao  1 Lần khiêu chiến lượt, khiêu chiến thất bại  Không tiêu hao  Khiêu chiến lượt &lt;br&gt;2. Mỗi cái cửa ải tại hoàn thành tam tinh mục tiêu sau sắp mở ra đối ứng  Càn quét  Công năng, mỗi lần càn quét tiêu hao  1 Nhiều lần số &lt;br&gt;3. Khiêu chiến lượt tại mỗi ngày  0 Điểm thiết lập lại , mỗi ngày nhưng tiêu hao Nguyên bảo hối đoái  2 Lần &lt;br&gt;4. Cần thông quan chương trước tất cả cửa ải hậu phương nhưng mở ra chương sau &lt;br&gt;5. Mỗi cái chương tiết có  10 Cái cửa ải, toàn bộ đánh bại hậu phương có thể thông qua nên chương tiết &lt;br&gt;6. Bộ phận chương tiết mở ra cần cái khác chương tiết thỏa mãn chỉ định số lượng Tinh cấp mục tiêu &lt;br&gt;7. Hoàn thành mỗi chương Tinh cấp mục tiêu có thể nhận được hi hữu mệnh cách thưởng</t>
+    <t xml:space="preserve">1. Mỗi lần khiêu chiến đều đem tiêu hao  1 Lần khiêu chiến lượt, khiêu chiến thất bại  Không tiêu hao  Khiêu chiến lượt &lt;br&gt;2. Mỗi cái cửa ải tại hoàn thành tam tinh mục tiêu sau sắp mở ra đối ứng  Càn quét  Công năng, mỗi lần càn quét tiêu hao  1 Nhiều lần số &lt;br&gt;3. Khiêu chiến lượt tại mỗi ngày  0 Điểm thiết lập lại , mỗi ngày nhưng tiêu hao Kim cương hối đoái  2 Lần &lt;br&gt;4. Cần thông quan chương trước tất cả cửa ải hậu phương nhưng mở ra chương sau &lt;br&gt;5. Mỗi cái chương tiết có  10 Cái cửa ải, toàn bộ đánh bại hậu phương có thể thông qua nên chương tiết &lt;br&gt;6. Bộ phận chương tiết mở ra cần cái khác chương tiết thỏa mãn chỉ định số lượng Tinh cấp mục tiêu &lt;br&gt;7. Hoàn thành mỗi chương Tinh cấp mục tiêu có thể nhận được hi hữu mệnh cách thưởng</t>
   </si>
   <si>
     <t xml:space="preserve">Sơn Hải kinh</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">Tinh anh điểm tướng xác suất</t>
   </si>
   <si>
-    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Phong thần thí luyện sẽ ở ngươi chơi cấp đạt tới  30 Cấp sau mở ra, hoạt động chu kỳ tiếp tục  21 Trời, quá thời hạn đem một lần nữa tuần hoàn.&lt;br&gt;2. Hoạt động trong lúc đó nhận được  Thí luyện điểm tích lũy  Càng nhiều, có thể nhận thưởng càng phong phú,  Thí luyện điểm tích lũy  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3.Thí luyện điểm tích lũy  Đồng dạng có thể thông qua tốn hao  Nguyên bảo  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa phong thần thí luyện tiến giai thưởng, càng có  Nguyên bảo  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động chu kỳ thiết lập lại sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
+    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Phong thần thí luyện sẽ ở ngươi chơi cấp đạt tới  30 Cấp sau mở ra, hoạt động chu kỳ tiếp tục  21 Trời, quá thời hạn đem một lần nữa tuần hoàn.&lt;br&gt;2. Hoạt động trong lúc đó nhận được  Thí luyện điểm tích lũy  Càng nhiều, có thể nhận thưởng càng phong phú,  Thí luyện điểm tích lũy  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3.Thí luyện điểm tích lũy  Đồng dạng có thể thông qua tốn hao  Kim cương  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa phong thần thí luyện tiến giai thưởng, càng có  Kim cương  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động chu kỳ thiết lập lại sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
   </si>
   <si>
     <t xml:space="preserve">Chiến lệnh</t>
@@ -1751,13 +1751,13 @@
     <t xml:space="preserve">Toàn bộ server hạn mua - Thứ hai tuần</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Hoạt động bắt đầu sau, mỗi vị người chơi sẽ có  1 Lần miễn phí nện trứng cơ hội &lt;br&gt;2. Hoạt động trong lúc đó, người chơi ở trong game tùy ý chỗ mỗi tiêu hao  2000 Nguyên bảo có thể đạt được  1 Lần nện trứng cơ hội, mỗi ngày nhiều nhất nhận được  5 Lần; Đồng thời hoạt động trong lúc đó người chơi mỗi thành công nạp tiền  50 Nguyên, cũng có thể nhận được  1 Lần nện trứng cơ hội, không thiết nhận được hạn mức cao nhất &lt;br&gt;3. Hoạt động kết thúc sau, như người chơi có còn thừa nện trứng cơ hội chưa sử dụng xong, thì mỗi còn thừa  1 Lần cơ hội sẽ thông qua bưu kiện trả về  200 Nguyên bảo</t>
+    <t xml:space="preserve">1. Hoạt động bắt đầu sau, mỗi vị người chơi sẽ có  1 Lần miễn phí nện trứng cơ hội &lt;br&gt;2. Hoạt động trong lúc đó, người chơi ở trong game tùy ý chỗ mỗi tiêu hao  2000 Kim cương có thể đạt được  1 Lần nện trứng cơ hội, mỗi ngày nhiều nhất nhận được  5 Lần; Đồng thời hoạt động trong lúc đó người chơi mỗi thành công nạp tiền  50 Nguyên, cũng có thể nhận được  1 Lần nện trứng cơ hội, không thiết nhận được hạn mức cao nhất &lt;br&gt;3. Hoạt động kết thúc sau, như người chơi có còn thừa nện trứng cơ hội chưa sử dụng xong, thì mỗi còn thừa  1 Lần cơ hội sẽ thông qua bưu kiện trả về  200 Kim cương</t>
   </si>
   <si>
     <t xml:space="preserve">Nện trứng</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Người chơi mỗi thành công nạp tiền  100 Nguyên hoặc là mỗi tiêu hao  5000 Nguyên bảo, đều có thể nhận được một tổ ngẫu nhiên ba chữ số dãy số, mỗi tổ dãy số đều có thể tại  Mã số của ta  Bên trong tiến hành một lần sửa chữa &lt;br&gt;2. Người chơi lựa chọn dãy số ba số lượng chữ cùng  Mở thưởng dãy số  Toàn bộ đối ứng, thì có thể đạt được giải đặc biệt; Người chơi lựa chọn dãy số vị thứ hai số cùng vị thứ ba số cùng  Mở thưởng dãy số  Đối ứng, thì có thể đạt được giải nhì; Người chơi lựa chọn dãy số vị thứ ba số cùng  Mở thưởng dãy số  Đối ứng, thì có thể đạt được tam đẳng thưởng ( Cần thiết phải chú ý sắp xếp trình tự, như sắp xếp trình tự không đối, thì không cách nào trúng thưởng )&lt;br&gt;3. Một hai ba chờ thưởng sẽ xuất hiện luân không, người chơi nhưng lặp lại lựa chọn một tổ dãy số; May mắn cá chép thưởng mỗi ngày tất nhiên sẽ có một vị người chơi nhận được &lt;br&gt;4. May mắn cá chép mở thưởng thời gian vì hoạt động trong lúc đó bên trong mỗi lúc trời tối  21:00 Cả, về sau nhận được dãy số người chơi sẽ tính toán tại ngày thứ hai trong hoạt động, ngày cuối cùng  21:00 Sau sẽ không nhận được dãy số</t>
+    <t xml:space="preserve">1. Người chơi mỗi thành công nạp tiền  100 Nguyên hoặc là mỗi tiêu hao  5000 Kim cương, đều có thể nhận được một tổ ngẫu nhiên ba chữ số dãy số, mỗi tổ dãy số đều có thể tại  Mã số của ta  Bên trong tiến hành một lần sửa chữa &lt;br&gt;2. Người chơi lựa chọn dãy số ba số lượng chữ cùng  Mở thưởng dãy số  Toàn bộ đối ứng, thì có thể đạt được giải đặc biệt; Người chơi lựa chọn dãy số vị thứ hai số cùng vị thứ ba số cùng  Mở thưởng dãy số  Đối ứng, thì có thể đạt được giải nhì; Người chơi lựa chọn dãy số vị thứ ba số cùng  Mở thưởng dãy số  Đối ứng, thì có thể đạt được tam đẳng thưởng ( Cần thiết phải chú ý sắp xếp trình tự, như sắp xếp trình tự không đối, thì không cách nào trúng thưởng )&lt;br&gt;3. Một hai ba chờ thưởng sẽ xuất hiện luân không, người chơi nhưng lặp lại lựa chọn một tổ dãy số; May mắn cá chép thưởng mỗi ngày tất nhiên sẽ có một vị người chơi nhận được &lt;br&gt;4. May mắn cá chép mở thưởng thời gian vì hoạt động trong lúc đó bên trong mỗi lúc trời tối  21:00 Cả, về sau nhận được dãy số người chơi sẽ tính toán tại ngày thứ hai trong hoạt động, ngày cuối cùng  21:00 Sau sẽ không nhận được dãy số</t>
   </si>
   <si>
     <t xml:space="preserve">May mắn cá chép</t>
@@ -1829,43 +1829,43 @@
     <t xml:space="preserve">Thang trời tranh bá - Cái khác</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Hoạt động trong lúc đó, tổng cộng có  7 Cái toàn bộ server BOSS, người chơi mỗi ngày có  2 Lần miễn phí khiêu chiến lượt, đồng thời nhưng tốn hao Nguyên bảo hối đoái lượt, mỗi lần khiêu chiến tổng cộng có  10 Hiệp khiêu chiến thời gian &lt;br&gt;2. Toàn bộ server BOSS HP hạ xuống đến nhất định tỉ lệ lúc, tất cả người chơi có thể nhận toàn bộ server thưởng, BOSS Bị đánh bại sau người chơi vẫn nhưng tiếp tục khiêu chiến nên BOSS, tổn thương lượng thưởng sẽ tại vượt thiên hậu thông qua bưu kiện gửi đi cho người chơi &lt;br&gt;4. Người chơi có thể hối đoái công kích tăng lên buff, hạn mức cao nhất  50%, này buff Chỉ nhằm vào người chơi mình, hôm sau sau buff Hiệu quả thanh không</t>
+    <t xml:space="preserve">1. Hoạt động trong lúc đó, tổng cộng có  7 Cái toàn bộ server BOSS, người chơi mỗi ngày có  2 Lần miễn phí khiêu chiến lượt, đồng thời nhưng tốn hao Kim cương hối đoái lượt, mỗi lần khiêu chiến tổng cộng có  10 Hiệp khiêu chiến thời gian &lt;br&gt;2. Toàn bộ server BOSS HP hạ xuống đến nhất định tỉ lệ lúc, tất cả người chơi có thể nhận toàn bộ server thưởng, BOSS Bị đánh bại sau người chơi vẫn nhưng tiếp tục khiêu chiến nên BOSS, tổn thương lượng thưởng sẽ tại vượt thiên hậu thông qua bưu kiện gửi đi cho người chơi &lt;br&gt;4. Người chơi có thể hối đoái công kích tăng lên buff, hạn mức cao nhất  50%, này buff Chỉ nhằm vào người chơi mình, hôm sau sau buff Hiệu quả thanh không</t>
   </si>
   <si>
     <t xml:space="preserve">Toàn bộ server BOSS</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mỗi kỳ hoạt động sẽ có  1 Vị chỉ định up Tướng, nhưng tiêu hao chỉ định đạo cụ cùng Nguyên bảo tiến hành triệu hoán &lt;br&gt;2. Hoạt động trong lúc đó triệu hoán có thể rút ra đến cao cấp thẻ trong ao tất cả tướng. Đồng thời,  Chỉ định up Tướng thu hoạch xác suất tăng lên trên diện rộng !&lt;br&gt;3. Hoạt động trong lúc đó, trước  {d} Lần triệu hoán chưa nhận được {s} Lúc, thứ  {d} Quất tất nhiên sẽ nhận được {s}; Tại trong lúc này rút trúng {s} Sau, còn thừa giữ gốc lượt sẽ thiết lập lại &lt;br&gt;5. Hoạt động kết thúc sau, chưa sử dụng xong đạo cụ nhưng tại ba lô bán ra</t>
+    <t xml:space="preserve">1. Mỗi kỳ hoạt động sẽ có  1 Vị chỉ định up Tướng, nhưng tiêu hao chỉ định đạo cụ cùng Kim cương tiến hành triệu hoán &lt;br&gt;2. Hoạt động trong lúc đó triệu hoán có thể rút ra đến cao cấp thẻ trong ao tất cả tướng. Đồng thời,  Chỉ định up Tướng thu hoạch xác suất tăng lên trên diện rộng !&lt;br&gt;3. Hoạt động trong lúc đó, trước  {d} Lần triệu hoán chưa nhận được {s} Lúc, thứ  {d} Quất tất nhiên sẽ nhận được {s}; Tại trong lúc này rút trúng {s} Sau, còn thừa giữ gốc lượt sẽ thiết lập lại &lt;br&gt;5. Hoạt động kết thúc sau, chưa sử dụng xong đạo cụ nhưng tại ba lô bán ra</t>
   </si>
   <si>
     <t xml:space="preserve">Hạn lúc triệu hoán xác suất</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tổng cộng có người, tiên, yêu, thần, ma  5 Đại chủng tộc tháp, thứ hai đến thứ sáu thay phiên mở ra, cuối tuần tất cả chủng tộc tháp đem toàn bộ mở ra &lt;br&gt;2. Người chơi mỗi ngày có thể thông quan cửa ải số vì  20 Quan &lt;br&gt;3. Đã thông quan tầng có thể tiến hành càn quét, mỗi ngày có  2 Lần miễn phí càn quét lượt.&lt;br&gt;4. Miễn phí càn quét lượt mỗi ngày  00:00 Đổi mới.&lt;br&gt;5. Nhưng tiêu hao  Nguyên bảo  Sau mua càn quét lượt, mỗi ngày hạn mua  2 Lần &lt;br&gt;6. Tại nhân tộc trong tháp, người chơi chỉ có thể ra trận đối ứng số lượng nhân tộc tướng.</t>
+    <t xml:space="preserve">1. Tổng cộng có người, tiên, yêu, thần, ma  5 Đại chủng tộc tháp, thứ hai đến thứ sáu thay phiên mở ra, cuối tuần tất cả chủng tộc tháp đem toàn bộ mở ra &lt;br&gt;2. Người chơi mỗi ngày có thể thông quan cửa ải số vì  20 Quan &lt;br&gt;3. Đã thông quan tầng có thể tiến hành càn quét, mỗi ngày có  2 Lần miễn phí càn quét lượt.&lt;br&gt;4. Miễn phí càn quét lượt mỗi ngày  00:00 Đổi mới.&lt;br&gt;5. Nhưng tiêu hao  Kim cương  Sau mua càn quét lượt, mỗi ngày hạn mua  2 Lần &lt;br&gt;6. Tại nhân tộc trong tháp, người chơi chỉ có thể ra trận đối ứng số lượng nhân tộc tướng.</t>
   </si>
   <si>
     <t xml:space="preserve">Chủng tộc tháp - Người</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tổng cộng có người, tiên, yêu, thần, ma  5 Đại chủng tộc tháp, thứ hai đến thứ sáu thay phiên mở ra, cuối tuần tất cả chủng tộc tháp đem toàn bộ mở ra &lt;br&gt;2. Người chơi mỗi ngày có thể thông quan cửa ải số vì  20 Quan &lt;br&gt;3. Đã thông quan tầng có thể tiến hành càn quét, mỗi ngày có  2 Lần miễn phí càn quét lượt.&lt;br&gt;4. Miễn phí càn quét lượt mỗi ngày  00:00 Đổi mới.&lt;br&gt;5. Nhưng tiêu hao  Nguyên bảo  Sau mua càn quét lượt, mỗi ngày hạn mua  2 Lần &lt;br&gt;6. Tại Tiên Tộc trong tháp, người chơi chỉ có thể ra trận đối ứng số lượng Tiên Tộc tướng.</t>
+    <t xml:space="preserve">1. Tổng cộng có người, tiên, yêu, thần, ma  5 Đại chủng tộc tháp, thứ hai đến thứ sáu thay phiên mở ra, cuối tuần tất cả chủng tộc tháp đem toàn bộ mở ra &lt;br&gt;2. Người chơi mỗi ngày có thể thông quan cửa ải số vì  20 Quan &lt;br&gt;3. Đã thông quan tầng có thể tiến hành càn quét, mỗi ngày có  2 Lần miễn phí càn quét lượt.&lt;br&gt;4. Miễn phí càn quét lượt mỗi ngày  00:00 Đổi mới.&lt;br&gt;5. Nhưng tiêu hao  Kim cương  Sau mua càn quét lượt, mỗi ngày hạn mua  2 Lần &lt;br&gt;6. Tại Tiên Tộc trong tháp, người chơi chỉ có thể ra trận đối ứng số lượng Tiên Tộc tướng.</t>
   </si>
   <si>
     <t xml:space="preserve">Chủng tộc tháp - Tiên</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tổng cộng có người, tiên, yêu, thần, ma  5 Đại chủng tộc tháp, thứ hai đến thứ sáu thay phiên mở ra, cuối tuần tất cả chủng tộc tháp đem toàn bộ mở ra &lt;br&gt;2. Người chơi mỗi ngày có thể thông quan cửa ải số vì  20 Quan &lt;br&gt;3. Đã thông quan tầng có thể tiến hành càn quét, mỗi ngày có  2 Lần miễn phí càn quét lượt.&lt;br&gt;4. Miễn phí càn quét lượt mỗi ngày  00:00 Đổi mới.&lt;br&gt;5. Nhưng tiêu hao  Nguyên bảo  Sau mua càn quét lượt, mỗi ngày hạn mua  2 Lần &lt;br&gt;6. Tại yêu tộc trong tháp, người chơi chỉ có thể ra trận đối ứng số lượng yêu tộc tướng.</t>
+    <t xml:space="preserve">1. Tổng cộng có người, tiên, yêu, thần, ma  5 Đại chủng tộc tháp, thứ hai đến thứ sáu thay phiên mở ra, cuối tuần tất cả chủng tộc tháp đem toàn bộ mở ra &lt;br&gt;2. Người chơi mỗi ngày có thể thông quan cửa ải số vì  20 Quan &lt;br&gt;3. Đã thông quan tầng có thể tiến hành càn quét, mỗi ngày có  2 Lần miễn phí càn quét lượt.&lt;br&gt;4. Miễn phí càn quét lượt mỗi ngày  00:00 Đổi mới.&lt;br&gt;5. Nhưng tiêu hao  Kim cương  Sau mua càn quét lượt, mỗi ngày hạn mua  2 Lần &lt;br&gt;6. Tại yêu tộc trong tháp, người chơi chỉ có thể ra trận đối ứng số lượng yêu tộc tướng.</t>
   </si>
   <si>
     <t xml:space="preserve">Chủng tộc tháp - Yêu</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tổng cộng có người, tiên, yêu, thần, ma  5 Đại chủng tộc tháp, thứ hai đến thứ sáu thay phiên mở ra, cuối tuần tất cả chủng tộc tháp đem toàn bộ mở ra &lt;br&gt;2. Người chơi mỗi ngày có thể thông quan cửa ải số vì  20 Quan &lt;br&gt;3. Đã thông quan tầng có thể tiến hành càn quét, mỗi ngày có  2 Lần miễn phí càn quét lượt.&lt;br&gt;4. Miễn phí càn quét lượt mỗi ngày  00:00 Đổi mới.&lt;br&gt;5. Nhưng tiêu hao  Nguyên bảo  Sau mua càn quét lượt, mỗi ngày hạn mua  2 Lần &lt;br&gt;6. Tại Thần tộc trong tháp, người chơi chỉ có thể ra trận đối ứng số lượng Thần tộc tướng.</t>
+    <t xml:space="preserve">1. Tổng cộng có người, tiên, yêu, thần, ma  5 Đại chủng tộc tháp, thứ hai đến thứ sáu thay phiên mở ra, cuối tuần tất cả chủng tộc tháp đem toàn bộ mở ra &lt;br&gt;2. Người chơi mỗi ngày có thể thông quan cửa ải số vì  20 Quan &lt;br&gt;3. Đã thông quan tầng có thể tiến hành càn quét, mỗi ngày có  2 Lần miễn phí càn quét lượt.&lt;br&gt;4. Miễn phí càn quét lượt mỗi ngày  00:00 Đổi mới.&lt;br&gt;5. Nhưng tiêu hao  Kim cương  Sau mua càn quét lượt, mỗi ngày hạn mua  2 Lần &lt;br&gt;6. Tại Thần tộc trong tháp, người chơi chỉ có thể ra trận đối ứng số lượng Thần tộc tướng.</t>
   </si>
   <si>
     <t xml:space="preserve">Chủng tộc tháp - Thần</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tổng cộng có người, tiên, yêu, thần, ma  5 Đại chủng tộc tháp, thứ hai đến thứ sáu thay phiên mở ra, cuối tuần tất cả chủng tộc tháp đem toàn bộ mở ra &lt;br&gt;2. Người chơi mỗi ngày có thể thông quan cửa ải số vì  20 Quan &lt;br&gt;3. Đã thông quan tầng có thể tiến hành càn quét, mỗi ngày có  2 Lần miễn phí càn quét lượt.&lt;br&gt;4. Miễn phí càn quét lượt mỗi ngày  00:00 Đổi mới.&lt;br&gt;5. Nhưng tiêu hao  Nguyên bảo  Sau mua càn quét lượt, mỗi ngày hạn mua  2 Lần &lt;br&gt;6. Tại ma tộc trong tháp, người chơi chỉ có thể ra trận đối ứng số lượng ma tộc tướng.</t>
+    <t xml:space="preserve">1. Tổng cộng có người, tiên, yêu, thần, ma  5 Đại chủng tộc tháp, thứ hai đến thứ sáu thay phiên mở ra, cuối tuần tất cả chủng tộc tháp đem toàn bộ mở ra &lt;br&gt;2. Người chơi mỗi ngày có thể thông quan cửa ải số vì  20 Quan &lt;br&gt;3. Đã thông quan tầng có thể tiến hành càn quét, mỗi ngày có  2 Lần miễn phí càn quét lượt.&lt;br&gt;4. Miễn phí càn quét lượt mỗi ngày  00:00 Đổi mới.&lt;br&gt;5. Nhưng tiêu hao  Kim cương  Sau mua càn quét lượt, mỗi ngày hạn mua  2 Lần &lt;br&gt;6. Tại ma tộc trong tháp, người chơi chỉ có thể ra trận đối ứng số lượng ma tộc tướng.</t>
   </si>
   <si>
     <t xml:space="preserve">Chủng tộc tháp - Ma</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">Cận Thiên Bảo hộp</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tham gia thiên giới mê cung, chiến thắng mỗi tầng cuối cùng BOSS Đem nhận được đối ứng mê cung điểm tích lũy cùng siêu giá trị thưởng. Trong đó tầng thứ nhất BOSS Điểm tích lũy vì  200, tầng thứ hai BOSS Điểm tích lũy vì  300, tầng thứ ba BOSS Điểm tích lũy vì  500.&lt;br&gt;2. Mê cung điểm tích lũy đồng dạng có thể thông qua tốn hao  Nguyên bảo  Phương thức hối đoái.&lt;br&gt;3. Trả tiền giải tỏa mê cung chiến lệnh tiến giai thưởng, càng có  Nguyên bảo , hi hữu vật liệu cùng xưng hào trực tiếp đưa.&lt;br&gt;4. Chiến lệnh hoạt động chu kỳ đem tiếp tục  30 Trời, nhưng mê cung chiến lệnh hữu hiệu thời gian lấy Chiến lệnh đếm ngược thời gian  Làm chuẩn, chu kỳ kết thúc sau, tích lũy cấp, kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời tham dự thiên giới mê cung nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
+    <t xml:space="preserve">1. Tham gia thiên giới mê cung, chiến thắng mỗi tầng cuối cùng BOSS Đem nhận được đối ứng mê cung điểm tích lũy cùng siêu giá trị thưởng. Trong đó tầng thứ nhất BOSS Điểm tích lũy vì  200, tầng thứ hai BOSS Điểm tích lũy vì  300, tầng thứ ba BOSS Điểm tích lũy vì  500.&lt;br&gt;2. Mê cung điểm tích lũy đồng dạng có thể thông qua tốn hao  Kim cương  Phương thức hối đoái.&lt;br&gt;3. Trả tiền giải tỏa mê cung chiến lệnh tiến giai thưởng, càng có  Kim cương , hi hữu vật liệu cùng xưng hào trực tiếp đưa.&lt;br&gt;4. Chiến lệnh hoạt động chu kỳ đem tiếp tục  30 Trời, nhưng mê cung chiến lệnh hữu hiệu thời gian lấy Chiến lệnh đếm ngược thời gian  Làm chuẩn, chu kỳ kết thúc sau, tích lũy cấp, kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời tham dự thiên giới mê cung nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
   </si>
   <si>
     <t xml:space="preserve">1.Nữ Oa thạch  Có thể để tất cả tướng ( Bao quát thuê tướng cùng bỏ mình tướng ) Khôi phục toàn bộ sinh mệnh.&lt;br&gt;2. Thông qua đạo cụ cửa hàng cùng diễn võ điểm tích lũy cửa hàng có thể nhận được  Nữ Oa thạch .&lt;br&gt;3. Chưa sử dụng  Nữ Oa thạch  Sẽ không theo thiên giới mê cung thiết lập lại mà biến mất.</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">Tướng phó tướng lựa chọn</t>
   </si>
   <si>
-    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Giải tỏa đêm lạnh chi kiếp chiến lệnh, trừ nhận được đối ứng cơ sở thưởng bên ngoài, còn có thể thu hoạch khen thưởng thêm.&lt;br&gt;2. Hoạt động trong lúc đó nhận được  Sương lạnh băng phách  Càng nhiều, có thể nhận thưởng càng phong phú,  Sương lạnh băng phách  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3.Sương lạnh băng phách  Đồng dạng có thể thông qua tốn hao  Nguyên bảo  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa đêm lạnh chi kiếp tiến giai thưởng, càng có  Nguyên bảo  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
+    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Giải tỏa đêm lạnh chi kiếp chiến lệnh, trừ nhận được đối ứng cơ sở thưởng bên ngoài, còn có thể thu hoạch khen thưởng thêm.&lt;br&gt;2. Hoạt động trong lúc đó nhận được  Sương lạnh băng phách  Càng nhiều, có thể nhận thưởng càng phong phú,  Sương lạnh băng phách  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3.Sương lạnh băng phách  Đồng dạng có thể thông qua tốn hao  Kim cương  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa đêm lạnh chi kiếp tiến giai thưởng, càng có  Kim cương  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
   </si>
   <si>
     <t xml:space="preserve">1. Man Hoang kỷ tổng cộng chia làm bảy quyển, mỗi quyển đều có ba vị Tiên gia trấn thủ, mỗi vị Tiên gia đều mang theo đại lượng bảo vật, đánh bại có thể đạt được thưởng &lt;br&gt;2. Man Hoang kỷ mỗi quyển đều có đơn độc khiêu chiến thời gian, người chơi tại trong thời gian quy định thành công khiêu chiến trước mắt quyển tất cả Tiên gia, thì sẽ tự động tiến vào quyển kế tiếp, lại còn thừa thời gian sẽ tích luỹ đến quyển kế tiếp. Như người chơi tại trong vòng thời gian quy định chưa hoàn thành khiêu chiến thì trước mắt quyển sẽ biến mất, tự động tiến vào quyển kế tiếp &lt;br&gt;3. Đương người chơi gặp được so sánh nan quan thẻ lúc, có thể lựa chọn buff Tăng cường thực lực, nhưng là tuyển lấy buff Sẽ mất đi phần thưởng nhất định, mời cẩn thận lựa chọn</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">Phụ ma dấu chấm hỏi</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tổng cộng có người, tiên, yêu, thần, ma  5 Đại quân đoàn phó bản, hoạt động trong lúc đó tất cả quân đoàn phó bản toàn bộ mở ra &lt;br&gt;2. Mỗi cái quân đoàn phó bản tổng cộng có  12 Tầng, mỗi tầng thông quan sau nhưng mở ra đối ứng càn quét công năng &lt;br&gt;3. Thành công khiêu chiến các chủng tộc quân đoàn phó bản về sau, sẽ rơi xuống đối ứng chủng tộc huy chương cùng tác chiến vật tư, chủng tộc huy chương có thể dùng tại hối đoái hi hữu đạo cụ, tác chiến vật tư có thể dùng tại hiến cho nhận được thưởng &lt;br&gt;4. Người chơi mỗi ngày sẽ có  5 Lần miễn phí khiêu chiến lượt, đồng thời mỗi ngày còn có thể hối đoái  5 Lần khiêu chiến lượt, hoạt động trong lúc đó người chơi còn có thể tiêu hao Nguyên bảo kích hoạt công kích buff</t>
+    <t xml:space="preserve">1. Tổng cộng có người, tiên, yêu, thần, ma  5 Đại quân đoàn phó bản, hoạt động trong lúc đó tất cả quân đoàn phó bản toàn bộ mở ra &lt;br&gt;2. Mỗi cái quân đoàn phó bản tổng cộng có  12 Tầng, mỗi tầng thông quan sau nhưng mở ra đối ứng càn quét công năng &lt;br&gt;3. Thành công khiêu chiến các chủng tộc quân đoàn phó bản về sau, sẽ rơi xuống đối ứng chủng tộc huy chương cùng tác chiến vật tư, chủng tộc huy chương có thể dùng tại hối đoái hi hữu đạo cụ, tác chiến vật tư có thể dùng tại hiến cho nhận được thưởng &lt;br&gt;4. Người chơi mỗi ngày sẽ có  5 Lần miễn phí khiêu chiến lượt, đồng thời mỗi ngày còn có thể hối đoái  5 Lần khiêu chiến lượt, hoạt động trong lúc đó người chơi còn có thể tiêu hao Kim cương kích hoạt công kích buff</t>
   </si>
   <si>
     <t xml:space="preserve">Quân đoàn xâm lấn</t>
@@ -2027,16 +2027,16 @@
     <t xml:space="preserve">Vượt phục lôi đài thi đấu - Thưởng tương quan</t>
   </si>
   <si>
-    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Ma đạo chí tôn thời gian hoạt động tiếp tục  14 Trời, quá thời hạn sau hoạt động đem kết thúc.&lt;br&gt;2. Hoạt động trong lúc đó nhận được  Ma xương  Càng nhiều, có thể nhận thưởng càng phong phú,  Ma xương  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3. Ma xương  Đồng dạng có thể thông qua tốn hao  Nguyên bảo  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa ma đạo chí tôn tiến giai thưởng, càng có  Nguyên bảo  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Thế giới cấp đạt tới  70 Cấp vượt phục tổ có thể tham gia này hoạt động &lt;br&gt;2. Như tại hoạt động trong lúc đó thế giới cấp đạt tới yêu cầu, đồng dạng có thể tham gia nên hoạt động, nhưng là sẽ chỉ ghi lại ở thế giới cấp đạt tới  70 Cấp sau Nguyên bảo tiêu hao, thế giới cấp  70 Cấp trước đó Nguyên bảo tiêu hao sẽ không ghi chép</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vượt phục Nguyên bảo xếp hạng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tại [ Trân bảo phường ] Bên trong, mỗi lần triệu hoán đều có xác suất nhận được đồ cất giữ, thông dụng Tiên Khí, chuyên môn Tiên Khí, chuyên môn Tiên Khí mảnh, cùng đỏ 1 Tinh trở lên trang bị &lt;br&gt;2. Hoạt động trong lúc đó nhưng tiêu hao chỉ định đạo cụ hoặc là Nguyên bảo tiến hành triệu hoán, mỗi 200 Quất tất nhiên sẽ triệu hồi ra chuẩn bị Tiên Khí hoặc là Thiên cấp mảnh, như tại trong lúc này thành công triệu hồi ra chuẩn bị Tiên Khí hoặc Thiên cấp mảnh, thì sẽ thiết lập lại mức tiến này &lt;br&gt;3. Hoạt động kết thúc sau, chưa sử dụng xong đạo cụ nhưng tại ba lô bán ra</t>
+    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Ma đạo chí tôn thời gian hoạt động tiếp tục  14 Trời, quá thời hạn sau hoạt động đem kết thúc.&lt;br&gt;2. Hoạt động trong lúc đó nhận được  Ma xương  Càng nhiều, có thể nhận thưởng càng phong phú,  Ma xương  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3. Ma xương  Đồng dạng có thể thông qua tốn hao  Kim cương  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa ma đạo chí tôn tiến giai thưởng, càng có  Kim cương  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Thế giới cấp đạt tới  70 Cấp vượt phục tổ có thể tham gia này hoạt động &lt;br&gt;2. Như tại hoạt động trong lúc đó thế giới cấp đạt tới yêu cầu, đồng dạng có thể tham gia nên hoạt động, nhưng là sẽ chỉ ghi lại ở thế giới cấp đạt tới  70 Cấp sau Kim cương tiêu hao, thế giới cấp  70 Cấp trước đó Kim cương tiêu hao sẽ không ghi chép</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vượt phục Kim cương xếp hạng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Tại [ Trân bảo phường ] Bên trong, mỗi lần triệu hoán đều có xác suất nhận được đồ cất giữ, thông dụng Tiên Khí, chuyên môn Tiên Khí, chuyên môn Tiên Khí mảnh, cùng đỏ 1 Tinh trở lên trang bị &lt;br&gt;2. Hoạt động trong lúc đó nhưng tiêu hao chỉ định đạo cụ hoặc là Kim cương tiến hành triệu hoán, mỗi 200 Quất tất nhiên sẽ triệu hồi ra chuẩn bị Tiên Khí hoặc là Thiên cấp mảnh, như tại trong lúc này thành công triệu hồi ra chuẩn bị Tiên Khí hoặc Thiên cấp mảnh, thì sẽ thiết lập lại mức tiến này &lt;br&gt;3. Hoạt động kết thúc sau, chưa sử dụng xong đạo cụ nhưng tại ba lô bán ra</t>
   </si>
   <si>
     <t xml:space="preserve">Trân bảo phường</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">1. Mỗi kỳ hoạt động tiếp tục  15 Trời,  15 Thiên hậu tự động mở ra vòng tiếp theo &lt;br&gt;2. Vòng tiếp theo hoạt động mở ra sau, sẽ thanh không người chơi trước đó tích lũy nạp tiền số trời</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Phổ thông tìm về  Không cần tốn hao Nguyên bảo nhưng là chỉ có thể tìm về 50% Tài nguyên.&lt;br&gt;2.Nguyên bảo tìm về  Cần tốn hao Nguyên bảo nhưng là có thể tìm về  100% Tài nguyên, Nguyên bảo tốn hao cùng tài nguyên tìm về công năng cùng tìm về lượt tương quan.&lt;br&gt;3. Cùng một loại phó bản tài nguyên chỉ có thể lựa chọn một loại tìm về phương thức.&lt;br&gt;4. Mỗi ngày  00:00 Thiết lập lại tài nguyên tìm về.</t>
+    <t xml:space="preserve">1. Phổ thông tìm về  Không cần tốn hao Kim cương nhưng là chỉ có thể tìm về 50% Tài nguyên.&lt;br&gt;2.Kim cương tìm về  Cần tốn hao Kim cương nhưng là có thể tìm về  100% Tài nguyên, Kim cương tốn hao cùng tài nguyên tìm về công năng cùng tìm về lượt tương quan.&lt;br&gt;3. Cùng một loại phó bản tài nguyên chỉ có thể lựa chọn một loại tìm về phương thức.&lt;br&gt;4. Mỗi ngày  00:00 Thiết lập lại tài nguyên tìm về.</t>
   </si>
   <si>
     <t xml:space="preserve">Tài nguyên tìm về</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">Mộng cảnh dấu chấm hỏi</t>
   </si>
   <si>
-    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Đột phá chi cảnh thời gian hoạt động tiếp tục  14 Trời, quá thời hạn sau hoạt động đem kết thúc.&lt;br&gt;2. Hoạt động trong lúc đó nhận được  Cảnh giới điểm tích lũy  Càng nhiều, có thể nhận thưởng càng phong phú,  Cảnh giới điểm tích lũy  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3. Cảnh giới điểm tích lũy  Đồng dạng có thể thông qua tốn hao  Nguyên bảo  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa đột phá chi cảnh tiến giai thưởng, càng có  Nguyên bảo  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
+    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Đột phá chi cảnh thời gian hoạt động tiếp tục  14 Trời, quá thời hạn sau hoạt động đem kết thúc.&lt;br&gt;2. Hoạt động trong lúc đó nhận được  Cảnh giới điểm tích lũy  Càng nhiều, có thể nhận thưởng càng phong phú,  Cảnh giới điểm tích lũy  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3. Cảnh giới điểm tích lũy  Đồng dạng có thể thông qua tốn hao  Kim cương  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa đột phá chi cảnh tiến giai thưởng, càng có  Kim cương  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
   </si>
   <si>
     <t xml:space="preserve">Vượt phục cấp thi đấu - Cơ sở quy tắc</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">Vượt phục cấp thi đấu - Thưởng nói rõ</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Người chơi mỗi ngày có được  3 Lần  Miễn phí xứng đôi lượt, xứng đôi một lần đối thủ tiêu hao  1 Điểm lượt ; Người chơi mỗi ngày còn có thể thông qua Nguyên bảo hối đoái xứng đôi lượt, mỗi ngày nhiều nhất hối đoái  5 Lần , miễn phí lượt tại mỗi ngày  00:00 Thiết lập lại.&lt;br&gt;2. Người chơi xứng đôi đến đối thủ sau sẽ tiến vào chuẩn bị giai đoạn, người chơi tại trong lúc này có thể điều chỉnh mình đội hình, lại tiến vào khiêu chiến.&lt;br&gt;3. Chiến đấu thắng lợi sau có thể nhận được nhất tinh, chiến đấu thất bại sẽ khấu trừ nhất tinh; Mặc kệ chiến đấu thắng lợi vẫn là thất bại đều đem nhận được chiến đấu thưởng.&lt;br&gt;4 Đầy tinh trạng thái dưới, người chơi đem phát động  Tấn cấp thi đấu ,  Tấn cấp thi đấu  Thắng lợi sau người chơi đem tấn thăng mới cấp.&lt;br&gt;5. Tại thông thường thi đấu bên trong vô luận chiến đấu thắng lợi vẫn là thất bại đều đem nhận được  Vinh quang điểm tích lũy ; Người chơi chiến đấu thất bại thì sẽ ưu tiên khấu trừ  Vinh quang điểm tích lũy , như  Vinh quang điểm tích lũy  Không đủ, thì khấu trừ người chơi nhất tinh.&lt;br&gt;6. Vinh quang điểm tích lũy  Hạn mức cao nhất vì  1200 Phân, phát động một lần cấp bảo hộ cần tiêu hao  300 Vinh quang điểm tích lũy .&lt;br&gt;7. Người chơi tại  Thanh đồng cùng bạch ngân cấp  Khiêu chiến thất bại sẽ không tổn thất tinh tinh, mời người chơi yên tâm chiến đấu!</t>
+    <t xml:space="preserve">1. Người chơi mỗi ngày có được  3 Lần  Miễn phí xứng đôi lượt, xứng đôi một lần đối thủ tiêu hao  1 Điểm lượt ; Người chơi mỗi ngày còn có thể thông qua Kim cương hối đoái xứng đôi lượt, mỗi ngày nhiều nhất hối đoái  5 Lần , miễn phí lượt tại mỗi ngày  00:00 Thiết lập lại.&lt;br&gt;2. Người chơi xứng đôi đến đối thủ sau sẽ tiến vào chuẩn bị giai đoạn, người chơi tại trong lúc này có thể điều chỉnh mình đội hình, lại tiến vào khiêu chiến.&lt;br&gt;3. Chiến đấu thắng lợi sau có thể nhận được nhất tinh, chiến đấu thất bại sẽ khấu trừ nhất tinh; Mặc kệ chiến đấu thắng lợi vẫn là thất bại đều đem nhận được chiến đấu thưởng.&lt;br&gt;4 Đầy tinh trạng thái dưới, người chơi đem phát động  Tấn cấp thi đấu ,  Tấn cấp thi đấu  Thắng lợi sau người chơi đem tấn thăng mới cấp.&lt;br&gt;5. Tại thông thường thi đấu bên trong vô luận chiến đấu thắng lợi vẫn là thất bại đều đem nhận được  Vinh quang điểm tích lũy ; Người chơi chiến đấu thất bại thì sẽ ưu tiên khấu trừ  Vinh quang điểm tích lũy , như  Vinh quang điểm tích lũy  Không đủ, thì khấu trừ người chơi nhất tinh.&lt;br&gt;6. Vinh quang điểm tích lũy  Hạn mức cao nhất vì  1200 Phân, phát động một lần cấp bảo hộ cần tiêu hao  300 Vinh quang điểm tích lũy .&lt;br&gt;7. Người chơi tại  Thanh đồng cùng bạch ngân cấp  Khiêu chiến thất bại sẽ không tổn thất tinh tinh, mời người chơi yên tâm chiến đấu!</t>
   </si>
   <si>
     <t xml:space="preserve">Cấp vừa xem</t>
@@ -2201,19 +2201,19 @@
     <t xml:space="preserve">Wechat chia sẻ dấu chấm hỏi</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tại [ Hạn lúc làn da diễn tiếp ] Bên trong, mỗi lần triệu hoán đều có xác suất nhận được linh môi ma nữ cùng Hỗn Thiên Đại Thánh tướng mảnh, linh môi ma nữ cùng Hỗn Thiên Đại Thánh chuyên môn Tiên Khí, chuyên môn Tiên Khí mảnh, cùng các loại bồi dưỡng vật liệu &lt;br&gt;2. Hoạt động trong lúc đó nhưng tiêu hao chỉ định đạo cụ hoặc là Nguyên bảo tiến hành triệu hoán, mỗi 200 Quất tất nhiên sẽ triệu hồi ra chuẩn bị Tiên Khí, Thiên cấp Tiên Khí mảnh cùng tướng bản thể, như tại trong lúc này thành công triệu hồi ra chuẩn bị Tiên Khí, Thiên cấp mảnh cùng tướng bản thể, thì sẽ thiết lập lại mức tiến này &lt;br&gt;3. Hoạt động kết thúc sau, chưa sử dụng xong đạo cụ nhưng tại ba lô bán ra</t>
+    <t xml:space="preserve">1. Tại [ Hạn lúc làn da diễn tiếp ] Bên trong, mỗi lần triệu hoán đều có xác suất nhận được linh môi ma nữ cùng Hỗn Thiên Đại Thánh tướng mảnh, linh môi ma nữ cùng Hỗn Thiên Đại Thánh chuyên môn Tiên Khí, chuyên môn Tiên Khí mảnh, cùng các loại bồi dưỡng vật liệu &lt;br&gt;2. Hoạt động trong lúc đó nhưng tiêu hao chỉ định đạo cụ hoặc là Kim cương tiến hành triệu hoán, mỗi 200 Quất tất nhiên sẽ triệu hồi ra chuẩn bị Tiên Khí, Thiên cấp Tiên Khí mảnh cùng tướng bản thể, như tại trong lúc này thành công triệu hồi ra chuẩn bị Tiên Khí, Thiên cấp mảnh cùng tướng bản thể, thì sẽ thiết lập lại mức tiến này &lt;br&gt;3. Hoạt động kết thúc sau, chưa sử dụng xong đạo cụ nhưng tại ba lô bán ra</t>
   </si>
   <si>
     <t xml:space="preserve">Vượt phục đúc lại tiêu hao</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tại xóa ngăn khảo thí trong lúc đó tham dự tinh anh kế phí khảo thí người sử dụng, tất cả nạp tiền sẽ ở không xóa ngăn nuốt vào tuyến lúc tiến hành trả về.&lt;br&gt;2. Tỷ như: Khảo thí phục bên trong nạp tiền 648RMB, sẽ ở không xóa ngăn phục trả về 648 Chờ trán thay mặt tệ +6480 Nguyên bảo + Nội trắc dũng giả ( Vĩnh cửu ) Xưng hào.&lt;br&gt;3. Chưa tiến hành nạp tiền người sử dụng cũng có thể lĩnh miễn phí vĩnh cửu xưng hào.</t>
+    <t xml:space="preserve">1. Tại xóa ngăn khảo thí trong lúc đó tham dự tinh anh kế phí khảo thí người sử dụng, tất cả nạp tiền sẽ ở không xóa ngăn nuốt vào tuyến lúc tiến hành trả về.&lt;br&gt;2. Tỷ như: Khảo thí phục bên trong nạp tiền 648RMB, sẽ ở không xóa ngăn phục trả về 648 Chờ trán thay mặt tệ +6480 Kim cương + Nội trắc dũng giả ( Vĩnh cửu ) Xưng hào.&lt;br&gt;3. Chưa tiến hành nạp tiền người sử dụng cũng có thể lĩnh miễn phí vĩnh cửu xưng hào.</t>
   </si>
   <si>
     <t xml:space="preserve">Quốc chiến dấu chấm hỏi 1</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Mỗi ngày chia sẻ: Mỗi ngày chia sẻ trò chơi kết nối, cái khác người sử dụng thông qua ngươi kết nối tiến vào trò chơi lúc tức tính làm xong thành mời, mời nhân số đạt tới mục tiêu lúc có thể nhận tương ứng thưởng.&lt;br&gt;2. Mời tân chú sách: Mới người sử dụng ( Chưa sáng tạo qua bất luận cái gì nhân vật ) Thông qua ngươi kết nối tiến vào trò chơi sau, tức tính làm xong thành 1 Cái mới người sử dụng mời, mời nhân số đạt tới mục tiêu liền có thể nhận tương ứng thưởng.&lt;br&gt;3. Chia sẻ hồng bao: Mỗi ngày thông qua người chơi khác chia sẻ kết nối tiến vào trò chơi lúc, liền có thể nhận hồng bao, mỗi ngày nhiều nhất 3 Lần.&lt;br&gt;4. Mời hảo hữu ( Thông qua ngươi kết nối tiến vào trò chơi lúc 5 Cấp trở xuống ) Đạt tới 30 Cấp: Mời mới người sử dụng nhân vật đạt tới 30 Cấp lúc liền có thể nhận thưởng, nhiều nhất mời 9 Người.&lt;br&gt;5. Mời hảo hữu ( Thông qua ngươi kết nối tiến vào trò chơi lúc 5 Cấp trở xuống ) Đạt tới 60 Cấp: Mời mới người sử dụng nhân vật đạt tới 60 Cấp lúc liền có thể nhận thưởng, nhiều nhất mời 9 Người.&lt;br&gt;6. Hảo hữu nạp tiền trở lại lợi: Mời hảo hữu ( Thông qua ngươi kết nối tiến vào trò chơi lúc 5 Cấp trở xuống ) Lần đầu nạp tiền lúc, ngươi đem nhận được nạp tiền kim ngạch X5 Nguyên bảo thưởng, nhiều nhất có thể đạt được 20 Lần trở lại lợi.</t>
+    <t xml:space="preserve">1. Mỗi ngày chia sẻ: Mỗi ngày chia sẻ trò chơi kết nối, cái khác người sử dụng thông qua ngươi kết nối tiến vào trò chơi lúc tức tính làm xong thành mời, mời nhân số đạt tới mục tiêu lúc có thể nhận tương ứng thưởng.&lt;br&gt;2. Mời tân chú sách: Mới người sử dụng ( Chưa sáng tạo qua bất luận cái gì nhân vật ) Thông qua ngươi kết nối tiến vào trò chơi sau, tức tính làm xong thành 1 Cái mới người sử dụng mời, mời nhân số đạt tới mục tiêu liền có thể nhận tương ứng thưởng.&lt;br&gt;3. Chia sẻ hồng bao: Mỗi ngày thông qua người chơi khác chia sẻ kết nối tiến vào trò chơi lúc, liền có thể nhận hồng bao, mỗi ngày nhiều nhất 3 Lần.&lt;br&gt;4. Mời hảo hữu ( Thông qua ngươi kết nối tiến vào trò chơi lúc 5 Cấp trở xuống ) Đạt tới 30 Cấp: Mời mới người sử dụng nhân vật đạt tới 30 Cấp lúc liền có thể nhận thưởng, nhiều nhất mời 9 Người.&lt;br&gt;5. Mời hảo hữu ( Thông qua ngươi kết nối tiến vào trò chơi lúc 5 Cấp trở xuống ) Đạt tới 60 Cấp: Mời mới người sử dụng nhân vật đạt tới 60 Cấp lúc liền có thể nhận thưởng, nhiều nhất mời 9 Người.&lt;br&gt;6. Hảo hữu nạp tiền trở lại lợi: Mời hảo hữu ( Thông qua ngươi kết nối tiến vào trò chơi lúc 5 Cấp trở xuống ) Lần đầu nạp tiền lúc, ngươi đem nhận được nạp tiền kim ngạch X5 Kim cương thưởng, nhiều nhất có thể đạt được 20 Lần trở lại lợi.</t>
   </si>
   <si>
     <t xml:space="preserve">Quốc chiến dấu chấm hỏi 2</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">Ràng buộc dấu chấm hỏi</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Thành trì chia làm:  Trận doanh đại bản doanh ,  Trung lập đại bản doanh ,  Phổ thông thành trì , trong đó  Trận doanh đại bản doanh  Vì người chơi chỗ trận doanh chân thực đại bản doanh, không thể bị công kích;Trung lập đại bản doanh  Thuộc tính cùng  Phổ thông thành trì  Đồng dạng nhưng bị công kích, nhưng tới láng giềng phe bạn thành trì sẽ tiêu trừ tứ cố vô thân trạng thái;Phổ thông thành trì  Có thể bị vừa đi vừa về tranh đoạt.&lt;br&gt;2. Giao chiến trạng thái: Đương thành trì bị công kích sau,  15 Phút bên trong thuộc về giao chiến trạng thái, di chuyển giao chiến trạng thái thành trì cần tiêu hao  1 Cái di chuyển khiến , giao chiến trạng thái dưới thành trì có hỏa diễm đặc hiệu biểu thị.&lt;br&gt;3. Ngẫu nhiên sự kiện: Mỗi   1 Giờ sẽ tại trừ đại bản doanh bên ngoài những thành trì khác ( Bao quát trung lập đại bản doanh ) Ngẫu nhiên đổi mới thưởng, chiếm lĩnh cai thành ao trận doanh người chơi mỗi  5 Phút Đều có thể ngoài định mức nhận được ích lợi.&lt;br&gt;4. Tứ cố vô thân: Đương thành trì cùng đại bản doanh không có kết nối thời điểm, lâm vào tứ cố vô thân bị vây quanh trạng thái, tứ cố vô thân thành trì có thể công kích liền nhau thành trì, nhưng không thể di chuyển, tứ cố vô thân trong thành trì người chơi thuộc tính sẽ diện rộng hạ thấp.&lt;br&gt;5. Kết minh: Nên có Server chiếm lĩnh lớn hơn hoặc bằng 10 Cái thành trì sau, hệ thống sẽ đem còn lại 3 Cái trận doanh liên minh, liên minh trong lúc đó thành trì cùng hưởng, minh hữu ở giữa không thể công kích lẫn nhau, đương liên minh trong thành viên có cái nào đó trận doanh chiếm lĩnh thành trì số lượng lớn hơn hoặc bằng 10 Cái lại cùng đối địch một cái trận doanh nhất trí lúc, sẽ so sánh hai cái này trận doanh điểm tích lũy trạng thái, điểm tích lũy cao sẽ bị đá ra liên minh, điểm tích lũy thấp sẽ tổ tiến liên minh. Đương 4 Cái trận doanh chiếm đoạt thành trì số lượng đều nhỏ hơn  10 Cái lúc, liên minh tự động giải tán.&lt;br&gt;6. Điểm tích lũy: Chiếm lĩnh thành trì sau mỗi 5 Phút Đều sẽ đạt được  Quân công  Lại chính mình sở tại trận doanh sẽ tích luỹ 1 Lần  Điểm tích lũy  Thưởng, lần đầu công chiếm trung lập đại bản doanh sẽ ngoài định mức nhận được điểm tích lũy, điểm tích lũy ảnh hưởng điểm tích lũy xếp hạng.&lt;br&gt;7. Công thành khiến: Tiến đánh những thành trì khác đạo cụ, mỗi 1 Giờ hồi phục 1 Cái, mỗi tuần ban đầu vì 5 Cái, offline thời gian cũng có thể tích luỹ, nhiều nhất nhưng tích luỹ 20 Cái, người chơi cũng có thể mỗi ngày tốn hao Nguyên bảo mua công thành khiến, VIP Cấp càng cao, có thể mua mua lượt càng nhiều.&lt;br&gt;8. Di chuyển khiến: Có thể dùng tại dời vào chiến loạn trạng thái thành trì, mỗi 3 Giờ hồi phục 1 Cái, mỗi tuần ban đầu vì 5 Cái, offline thời gian cũng có thể tích luỹ, nhiều nhất nhưng tích luỹ 20 Cái, người chơi cũng có thể mỗi ngày tốn hao Nguyên bảo mua di chuyển khiến, VIP Cấp càng cao, có thể mua mua lượt càng nhiều.&lt;br&gt;9. Sau khi chiến đấu kết thúc, như phòng thủ phương thắng lợi, phòng thủ tướng sẽ kế thừa lần trước chiến đấu HP còn thừa tỉ lệ phần trăm; Phòng thủ phương di chuyển thành trì sau nhưng khôi phục HP.</t>
+    <t xml:space="preserve">1. Thành trì chia làm:  Trận doanh đại bản doanh ,  Trung lập đại bản doanh ,  Phổ thông thành trì , trong đó  Trận doanh đại bản doanh  Vì người chơi chỗ trận doanh chân thực đại bản doanh, không thể bị công kích;Trung lập đại bản doanh  Thuộc tính cùng  Phổ thông thành trì  Đồng dạng nhưng bị công kích, nhưng tới láng giềng phe bạn thành trì sẽ tiêu trừ tứ cố vô thân trạng thái;Phổ thông thành trì  Có thể bị vừa đi vừa về tranh đoạt.&lt;br&gt;2. Giao chiến trạng thái: Đương thành trì bị công kích sau,  15 Phút bên trong thuộc về giao chiến trạng thái, di chuyển giao chiến trạng thái thành trì cần tiêu hao  1 Cái di chuyển khiến , giao chiến trạng thái dưới thành trì có hỏa diễm đặc hiệu biểu thị.&lt;br&gt;3. Ngẫu nhiên sự kiện: Mỗi   1 Giờ sẽ tại trừ đại bản doanh bên ngoài những thành trì khác ( Bao quát trung lập đại bản doanh ) Ngẫu nhiên đổi mới thưởng, chiếm lĩnh cai thành ao trận doanh người chơi mỗi  5 Phút Đều có thể ngoài định mức nhận được ích lợi.&lt;br&gt;4. Tứ cố vô thân: Đương thành trì cùng đại bản doanh không có kết nối thời điểm, lâm vào tứ cố vô thân bị vây quanh trạng thái, tứ cố vô thân thành trì có thể công kích liền nhau thành trì, nhưng không thể di chuyển, tứ cố vô thân trong thành trì người chơi thuộc tính sẽ diện rộng hạ thấp.&lt;br&gt;5. Kết minh: Nên có Server chiếm lĩnh lớn hơn hoặc bằng 10 Cái thành trì sau, hệ thống sẽ đem còn lại 3 Cái trận doanh liên minh, liên minh trong lúc đó thành trì cùng hưởng, minh hữu ở giữa không thể công kích lẫn nhau, đương liên minh trong thành viên có cái nào đó trận doanh chiếm lĩnh thành trì số lượng lớn hơn hoặc bằng 10 Cái lại cùng đối địch một cái trận doanh nhất trí lúc, sẽ so sánh hai cái này trận doanh điểm tích lũy trạng thái, điểm tích lũy cao sẽ bị đá ra liên minh, điểm tích lũy thấp sẽ tổ tiến liên minh. Đương 4 Cái trận doanh chiếm đoạt thành trì số lượng đều nhỏ hơn  10 Cái lúc, liên minh tự động giải tán.&lt;br&gt;6. Điểm tích lũy: Chiếm lĩnh thành trì sau mỗi 5 Phút Đều sẽ đạt được  Quân công  Lại chính mình sở tại trận doanh sẽ tích luỹ 1 Lần  Điểm tích lũy  Thưởng, lần đầu công chiếm trung lập đại bản doanh sẽ ngoài định mức nhận được điểm tích lũy, điểm tích lũy ảnh hưởng điểm tích lũy xếp hạng.&lt;br&gt;7. Công thành khiến: Tiến đánh những thành trì khác đạo cụ, mỗi 1 Giờ hồi phục 1 Cái, mỗi tuần ban đầu vì 5 Cái, offline thời gian cũng có thể tích luỹ, nhiều nhất nhưng tích luỹ 20 Cái, người chơi cũng có thể mỗi ngày tốn hao Kim cương mua công thành khiến, VIP Cấp càng cao, có thể mua mua lượt càng nhiều.&lt;br&gt;8. Di chuyển khiến: Có thể dùng tại dời vào chiến loạn trạng thái thành trì, mỗi 3 Giờ hồi phục 1 Cái, mỗi tuần ban đầu vì 5 Cái, offline thời gian cũng có thể tích luỹ, nhiều nhất nhưng tích luỹ 20 Cái, người chơi cũng có thể mỗi ngày tốn hao Kim cương mua di chuyển khiến, VIP Cấp càng cao, có thể mua mua lượt càng nhiều.&lt;br&gt;9. Sau khi chiến đấu kết thúc, như phòng thủ phương thắng lợi, phòng thủ tướng sẽ kế thừa lần trước chiến đấu HP còn thừa tỉ lệ phần trăm; Phòng thủ phương di chuyển thành trì sau nhưng khôi phục HP.</t>
   </si>
   <si>
     <t xml:space="preserve">Tiên Khí đổi thành</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">Triệu hoán phúc lợi - Phần mềm nhỏ</t>
   </si>
   <si>
-    <t xml:space="preserve">Thiết lập lại PVP Thuộc tính cần tiêu hao  {s} Nguyên bảo , thiết lập lại sau trước mắt nghề nghiệp PVP Thuộc tính cấp đem bị thanh không ( Biến thành chưa kích hoạt trạng thái ), đồng thời  100% Trả về tiêu hao dưỡng thành vật liệu. Mời thận trọng cân nhắc!</t>
+    <t xml:space="preserve">Thiết lập lại PVP Thuộc tính cần tiêu hao  {s} Kim cương , thiết lập lại sau trước mắt nghề nghiệp PVP Thuộc tính cấp đem bị thanh không ( Biến thành chưa kích hoạt trạng thái ), đồng thời  100% Trả về tiêu hao dưỡng thành vật liệu. Mời thận trọng cân nhắc!</t>
   </si>
   <si>
     <t xml:space="preserve">Đoán xâm phúc lợi - Phần mềm nhỏ</t>
   </si>
   <si>
-    <t xml:space="preserve">Lãng quên PVP Kỹ năng cần tiêu hao  {s} Nguyên bảo , kỹ năng lãng quên sau kỹ năng cấp đem thiết lập lại vì  1 Cấp , đồng thời  100% Trả về tiêu hao dưỡng thành vật liệu. Phải chăng lựa chọn lãng quên kỹ năng!</t>
+    <t xml:space="preserve">Lãng quên PVP Kỹ năng cần tiêu hao  {s} Kim cương , kỹ năng lãng quên sau kỹ năng cấp đem thiết lập lại vì  1 Cấp , đồng thời  100% Trả về tiêu hao dưỡng thành vật liệu. Phải chăng lựa chọn lãng quên kỹ năng!</t>
   </si>
   <si>
     <t xml:space="preserve">Long Tước chi tư</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">Trân tàng bảo hạp</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Có được 1 Cái đã tiến giai thú hồn liền có thể mở ra nên loại thú hồn cộng minh giao diện &lt;br&gt;2. Tiến giai qua đồng loại thú hồn bên trong cấp tối cao thú hồn sẽ tự động trở thành cộng minh chủ thể, cấp đem làm cộng minh thủy tinh cấp &lt;br&gt;3. Cộng minh cột vị bên trong có thể để vào đã tiến giai đồng loại thú hồn, để vào sau cấp đem tự động tăng lên đến cộng minh thủy tinh cấp, nhưng tăng lên cấp hạn mức cao nhất thụ thú hồn cấp số ảnh hưởng.&lt;br&gt;4. Đã tiến giai thú hồn để vào cột vị sau, thú này hồn thì không thể thăng cấp, không thể cản làm thôn phệ cùng tiến giai vật liệu, nhưng có thể bình thường sử dụng cùng thú hồn tẩy luyện &lt;br&gt;5. Cột vị mở ra cần tiêu hao  Cộng minh thủy tinh &lt;br&gt;6. Đương thú hồn rời đi cột vị lúc, cột vị sẽ tiến vào  24 Giờ thời gian cooldown, có thể tốn hao Nguyên bảo đổi mới thời gian cooldown</t>
+    <t xml:space="preserve">1. Có được 1 Cái đã tiến giai thú hồn liền có thể mở ra nên loại thú hồn cộng minh giao diện &lt;br&gt;2. Tiến giai qua đồng loại thú hồn bên trong cấp tối cao thú hồn sẽ tự động trở thành cộng minh chủ thể, cấp đem làm cộng minh thủy tinh cấp &lt;br&gt;3. Cộng minh cột vị bên trong có thể để vào đã tiến giai đồng loại thú hồn, để vào sau cấp đem tự động tăng lên đến cộng minh thủy tinh cấp, nhưng tăng lên cấp hạn mức cao nhất thụ thú hồn cấp số ảnh hưởng.&lt;br&gt;4. Đã tiến giai thú hồn để vào cột vị sau, thú này hồn thì không thể thăng cấp, không thể cản làm thôn phệ cùng tiến giai vật liệu, nhưng có thể bình thường sử dụng cùng thú hồn tẩy luyện &lt;br&gt;5. Cột vị mở ra cần tiêu hao  Cộng minh thủy tinh &lt;br&gt;6. Đương thú hồn rời đi cột vị lúc, cột vị sẽ tiến vào  24 Giờ thời gian cooldown, có thể tốn hao Kim cương đổi mới thời gian cooldown</t>
   </si>
   <si>
     <t xml:space="preserve">Điển tàng bảo hạp</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">Vượt phục PVP- Chủ bảng</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Phong Thần đài mở ra sau tự động lựa chọn năm cấp bậc tối cao tướng làm cung phụng tướng, năm trong đó  Cấp thấp nhất  Làm Phong Thần đài cấp &lt;br&gt;2. Để vào phía dưới cột vị bên trong tướng cấp tự động tăng lên đến Phong Thần đài cấp, cấp số cũng tự động tăng lên đến cùng cung phụng tướng bên trong cấp thấp nhất tướng giống nhau, cũng kích hoạt đối ứng kỹ năng cùng thuộc tính tăng thêm. Sau khi tăng lên tướng cấp cùng cấp số vẫn nhận tướng phẩm chất hạn chế &lt;br&gt;3. Để vào phía dưới cột vị tướng có thể thăng tinh, nhưng là cấm chỉ thăng cấp, cấm chỉ làm thăng tinh vật liệu, không cách nào tiến hành dung hợp, hiến tế, lui trở về chờ thao tác &lt;br&gt;4. Đương cột vị bên trong tướng rời đi sau, cột vị sẽ tiến vào 24 Giờ làm lạnh, làm lạnh hoàn tất sau mới có thể để vào mới tướng &lt;br&gt;5. Người chơi nhưng tiêu hao anh linh mảnh đổi mới cột vị thời gian cooldown, anh linh mảnh tại thông quan 50 Cấp lịch luyện sau nhưng treo máy nhận được &lt;br&gt;6. Đương năm cái cho phụng tướng đều đến 340 Cấp, cái này năm tướng đem hoàn nguyên đến 1 Cấp, cũng tự động để vào Phong Thần đài tướng cột bên trong ( Hệ thống đưa tặng năm tướng cột vị ), năm vị cung phụng tướng thăng cấp tài nguyên sẽ không trả về, từ đó đổi lấy Phong Thần đài đột phá 340 Cấp cấp hạn mức cao nhất &lt;br&gt;7. Phong Thần đài đột phá 340 Cấp hạn mức cao nhất sau, sẽ không còn ỷ lại cung phụng tướng tăng lên cấp. Nhưng tiêu hao tài nguyên đem Phong Thần đài cấp, cột vị bên trong tướng đem tùy theo đồng bộ tăng lên cấp &lt;br&gt;8. Phong Thần đài cấp hạn mức cao nhất từ người chơi bồi dưỡng được  12/13/14 Tinh nhân vật số lượng quyết định, mỗi một cái  12/13/14 Tinh nhân vật, vì Phong Thần đài gia tăng  2/4/6 Cấp hạn mức cao nhất &lt;br&gt;9. Tướng cột vị nhưng tiêu hao  Anh linh mảnh  Hoặc  Nguyên bảo  Mở rộng, anh linh mảnh tại lịch luyện chủ tuyến treo máy bên trong nhận được</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Mỗi  Thứ sáu 20 Điểm đến  Thứ bảy 20 Điểm có thể đối vượt phục PVP32 Cường đội ngũ tiến hành  Quan ,  Á ,  Quý  Quân cạnh đoán.&lt;br&gt;2. Cạnh đoán cần tốn hao nhất định Nguyên bảo, đoán đúng nhưng  Gấp bội  Trả về, đoán sai đem  Toàn bộ khấu trừ .&lt;br&gt;3. Chỉ có thể đối trong đó  1 Chi đội ngũ cạnh đoán  1 Loại thứ tự.&lt;br&gt;4. Chỉ có thể ở cạnh đoán trong lúc đó tiến hành cạnh đoán.&lt;br&gt;5. Cuối cùng thưởng sẽ tại đấu vòng loại kết thúc sau từ  Bưu kiện  Cấp cho.</t>
+    <t xml:space="preserve">1. Phong Thần đài mở ra sau tự động lựa chọn năm cấp bậc tối cao tướng làm cung phụng tướng, năm trong đó  Cấp thấp nhất  Làm Phong Thần đài cấp &lt;br&gt;2. Để vào phía dưới cột vị bên trong tướng cấp tự động tăng lên đến Phong Thần đài cấp, cấp số cũng tự động tăng lên đến cùng cung phụng tướng bên trong cấp thấp nhất tướng giống nhau, cũng kích hoạt đối ứng kỹ năng cùng thuộc tính tăng thêm. Sau khi tăng lên tướng cấp cùng cấp số vẫn nhận tướng phẩm chất hạn chế &lt;br&gt;3. Để vào phía dưới cột vị tướng có thể thăng tinh, nhưng là cấm chỉ thăng cấp, cấm chỉ làm thăng tinh vật liệu, không cách nào tiến hành dung hợp, hiến tế, lui trở về chờ thao tác &lt;br&gt;4. Đương cột vị bên trong tướng rời đi sau, cột vị sẽ tiến vào 24 Giờ làm lạnh, làm lạnh hoàn tất sau mới có thể để vào mới tướng &lt;br&gt;5. Người chơi nhưng tiêu hao anh linh mảnh đổi mới cột vị thời gian cooldown, anh linh mảnh tại thông quan 50 Cấp lịch luyện sau nhưng treo máy nhận được &lt;br&gt;6. Đương năm cái cho phụng tướng đều đến 340 Cấp, cái này năm tướng đem hoàn nguyên đến 1 Cấp, cũng tự động để vào Phong Thần đài tướng cột bên trong ( Hệ thống đưa tặng năm tướng cột vị ), năm vị cung phụng tướng thăng cấp tài nguyên sẽ không trả về, từ đó đổi lấy Phong Thần đài đột phá 340 Cấp cấp hạn mức cao nhất &lt;br&gt;7. Phong Thần đài đột phá 340 Cấp hạn mức cao nhất sau, sẽ không còn ỷ lại cung phụng tướng tăng lên cấp. Nhưng tiêu hao tài nguyên đem Phong Thần đài cấp, cột vị bên trong tướng đem tùy theo đồng bộ tăng lên cấp &lt;br&gt;8. Phong Thần đài cấp hạn mức cao nhất từ người chơi bồi dưỡng được  12/13/14 Tinh nhân vật số lượng quyết định, mỗi một cái  12/13/14 Tinh nhân vật, vì Phong Thần đài gia tăng  2/4/6 Cấp hạn mức cao nhất &lt;br&gt;9. Tướng cột vị nhưng tiêu hao  Anh linh mảnh  Hoặc  Kim cương  Mở rộng, anh linh mảnh tại lịch luyện chủ tuyến treo máy bên trong nhận được</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mỗi  Thứ sáu 20 Điểm đến  Thứ bảy 20 Điểm có thể đối vượt phục PVP32 Cường đội ngũ tiến hành  Quan ,  Á ,  Quý  Quân cạnh đoán.&lt;br&gt;2. Cạnh đoán cần tốn hao nhất định Kim cương, đoán đúng nhưng  Gấp bội  Trả về, đoán sai đem  Toàn bộ khấu trừ .&lt;br&gt;3. Chỉ có thể đối trong đó  1 Chi đội ngũ cạnh đoán  1 Loại thứ tự.&lt;br&gt;4. Chỉ có thể ở cạnh đoán trong lúc đó tiến hành cạnh đoán.&lt;br&gt;5. Cuối cùng thưởng sẽ tại đấu vòng loại kết thúc sau từ  Bưu kiện  Cấp cho.</t>
   </si>
   <si>
     <t xml:space="preserve">Tết xuân hoạt động</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">Trồng cây tiết</t>
   </si>
   <si>
-    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Nguyên kế hoạch thời gian hoạt động tiếp tục  14 Trời, quá thời hạn sau hoạt động đem kết thúc.&lt;br&gt;2. Hoạt động trong lúc đó nhận được  Phong Hỏa Luân  Càng nhiều, có thể nhận thưởng càng phong phú,  Phong Hỏa Luân  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3. Phong Hỏa Luân  Đồng dạng có thể thông qua tốn hao  Nguyên bảo  Phương thức mua.&lt;br&gt;4. Trả tiền giải tỏa nguyên kế hoạch tiến giai thưởng, càng có  Nguyên bảo  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
+    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Nguyên kế hoạch thời gian hoạt động tiếp tục  14 Trời, quá thời hạn sau hoạt động đem kết thúc.&lt;br&gt;2. Hoạt động trong lúc đó nhận được  Phong Hỏa Luân  Càng nhiều, có thể nhận thưởng càng phong phú,  Phong Hỏa Luân  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3. Phong Hỏa Luân  Đồng dạng có thể thông qua tốn hao  Kim cương  Phương thức mua.&lt;br&gt;4. Trả tiền giải tỏa nguyên kế hoạch tiến giai thưởng, càng có  Kim cương  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
   </si>
   <si>
     <t xml:space="preserve">Bày trận</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">Thú linh</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Hoạt động trong lúc đó, người chơi có thể thông qua trồng cây đến nhận được thưởng, khác biệt cây giống thành thục thời gian khác biệt, tương ứng thưởng cũng có chỗ khác biệt.&lt;br&gt;2. Người chơi nhưng tiêu hao Nguyên bảo đến xây dựng thêm thổ địa, thổ địa càng nhiều, có thể gieo trồng cây giống càng nhiều &lt;br&gt;3. Người chơi còn có thể tưới nước đến rút ngắn cây giống thành thục thời gian, cây giống thành thục sau.&lt;br&gt;4.Cây giống  Cùng  Ấm nước  Là hạn lúc đạo cụ, hoạt động kết thúc sau đạo cụ sẽ biến mất, mời kịp thời sử dụng!&lt;br&gt;5.Cây hạnh mầm  Nhưng tại cần cù chăm chỉ bên trong nhận được,  Cây hòe mầm  Cùng  Ấm nước  Nhưng tại trồng cây gói quà bên trong nhận được.</t>
+    <t xml:space="preserve">1. Hoạt động trong lúc đó, người chơi có thể thông qua trồng cây đến nhận được thưởng, khác biệt cây giống thành thục thời gian khác biệt, tương ứng thưởng cũng có chỗ khác biệt.&lt;br&gt;2. Người chơi nhưng tiêu hao Kim cương đến xây dựng thêm thổ địa, thổ địa càng nhiều, có thể gieo trồng cây giống càng nhiều &lt;br&gt;3. Người chơi còn có thể tưới nước đến rút ngắn cây giống thành thục thời gian, cây giống thành thục sau.&lt;br&gt;4.Cây giống  Cùng  Ấm nước  Là hạn lúc đạo cụ, hoạt động kết thúc sau đạo cụ sẽ biến mất, mời kịp thời sử dụng!&lt;br&gt;5.Cây hạnh mầm  Nhưng tại cần cù chăm chỉ bên trong nhận được,  Cây hòe mầm  Cùng  Ấm nước  Nhưng tại trồng cây gói quà bên trong nhận được.</t>
   </si>
   <si>
     <t xml:space="preserve">Giữa xuân chi nguyệt</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">Trở về chiến lệnh</t>
   </si>
   <si>
-    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Sử dụng  Nhiều  Cái giống nhau cấp thấp vật liệu, có thể hợp thành cao cấp hơn vật liệu &lt;br&gt;2. Hợp thành cao cấp vật liệu lúc, cần tiêu hao Nguyên bảo, hợp thành vật liệu càng cao cấp hơn, tiêu hao Nguyên bảo càng nhiều &lt;br&gt;3. Hợp thành cao cấp vật liệu số lượng càng nhiều, tiêu hao Nguyên bảo càng nhiều</t>
+    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Sử dụng  Nhiều  Cái giống nhau cấp thấp vật liệu, có thể hợp thành cao cấp hơn vật liệu &lt;br&gt;2. Hợp thành cao cấp vật liệu lúc, cần tiêu hao Kim cương, hợp thành vật liệu càng cao cấp hơn, tiêu hao Kim cương càng nhiều &lt;br&gt;3. Hợp thành cao cấp vật liệu số lượng càng nhiều, tiêu hao Kim cương càng nhiều</t>
   </si>
   <si>
     <t xml:space="preserve">Hoa tươi lễ vật</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">Thú linh ra trận</t>
   </si>
   <si>
-    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Hoạt động trong lúc đó nhận được  Trở về điểm tích lũy  Càng nhiều, có thể nhận thưởng càng phong phú,  Trở về điểm tích lũy  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3.Trở về điểm tích lũy  Đồng dạng có thể thông qua tốn hao  Nguyên bảo  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa trở về chiến lệnh tiến giai thưởng, càng có  Nguyên bảo  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
+    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Hoạt động trong lúc đó nhận được  Trở về điểm tích lũy  Càng nhiều, có thể nhận thưởng càng phong phú,  Trở về điểm tích lũy  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3.Trở về điểm tích lũy  Đồng dạng có thể thông qua tốn hao  Kim cương  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa trở về chiến lệnh tiến giai thưởng, càng có  Kim cương  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
   </si>
   <si>
     <t xml:space="preserve">Sáu một boss</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">Tướng kế thừa dưới đáy</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Cạnh đoán tỉ lệ đặt cược  Căn cứ tập trung nên tuyển thủ dự thi người chơi số lượng biến hóa &lt;br&gt;2.Cuối cùng tỉ lệ đặt cược  Căn cứ người chơi tập trung lúc Server tỉ lệ đặt cược làm chuẩn, bởi vì tập trung nhân số thời gian thực biến hóa,  Cuối cùng tỉ lệ đặt cược  Cùng giao diện biểu hiện khả năng có điều khác biệt &lt;br&gt;3. Cạnh đoán sau, nếu như đoán đúng, căn cứ tập trung  Nguyên bảo , Nguyên bảo cùng Võ Thần điểm tích lũy  Hối đoái tỉ lệ  Cùng trả về  Tỉ lệ đặt cược , cuối cùng nhận được  Võ Thần điểm tích lũy  Làm thưởng. Thưởng thông qua bưu kiện cấp cho.</t>
+    <t xml:space="preserve">1. Cạnh đoán tỉ lệ đặt cược  Căn cứ tập trung nên tuyển thủ dự thi người chơi số lượng biến hóa &lt;br&gt;2.Cuối cùng tỉ lệ đặt cược  Căn cứ người chơi tập trung lúc Server tỉ lệ đặt cược làm chuẩn, bởi vì tập trung nhân số thời gian thực biến hóa,  Cuối cùng tỉ lệ đặt cược  Cùng giao diện biểu hiện khả năng có điều khác biệt &lt;br&gt;3. Cạnh đoán sau, nếu như đoán đúng, căn cứ tập trung  Kim cương , Kim cương cùng Võ Thần điểm tích lũy  Hối đoái tỉ lệ  Cùng trả về  Tỉ lệ đặt cược , cuối cùng nhận được  Võ Thần điểm tích lũy  Làm thưởng. Thưởng thông qua bưu kiện cấp cho.</t>
   </si>
   <si>
     <t xml:space="preserve">Trăm quất</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">Tướng thí luyện</t>
   </si>
   <si>
-    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Thần long khế ước sẽ ở ngươi chơi cấp đạt tới  80 Cấp sau mở ra &lt;br&gt;2. Hoạt động trong lúc đó nhận được  Thần long điểm tích lũy  Càng nhiều, có thể nhận thưởng càng phong phú,  Thần long điểm tích lũy  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3. Thần long điểm tích lũy  Đồng dạng có thể thông qua tốn hao  Nguyên bảo  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa khế ước tiến giai thưởng, càng có  Nguyên bảo  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
+    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Thần long khế ước sẽ ở ngươi chơi cấp đạt tới  80 Cấp sau mở ra &lt;br&gt;2. Hoạt động trong lúc đó nhận được  Thần long điểm tích lũy  Càng nhiều, có thể nhận thưởng càng phong phú,  Thần long điểm tích lũy  Có thể từ hoàn thành mỗi ngày nhiệm vụ, mỗi tuần nhiệm vụ bên trong nhận được.&lt;br&gt;3. Thần long điểm tích lũy  Đồng dạng có thể thông qua tốn hao  Kim cương  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa khế ước tiến giai thưởng, càng có  Kim cương  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
   </si>
   <si>
     <t xml:space="preserve">Thí luyện hào lễ</t>
   </si>
   <si>
-    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Hoạt động trong lúc đó người chơi mỗi ngày có  2 Lần cơ hội khiêu chiến, đồng thời mỗi ngày còn có thể Nguyên bảo mua khiêu chiến lượt &lt;br&gt;2. Hoạt động tổng cộng có  10 Cái cửa ải, mỗi thông qua một quan sẽ nhận được tương ứng điểm tích lũy, nhận được nhất định điểm tích lũy có thể nhận chỉ định thưởng</t>
+    <t xml:space="preserve">Quy tắc nói rõ: &lt;br&gt;1. Hoạt động trong lúc đó người chơi mỗi ngày có  2 Lần cơ hội khiêu chiến, đồng thời mỗi ngày còn có thể Kim cương mua khiêu chiến lượt &lt;br&gt;2. Hoạt động tổng cộng có  10 Cái cửa ải, mỗi thông qua một quan sẽ nhận được tương ứng điểm tích lũy, nhận được nhất định điểm tích lũy có thể nhận chỉ định thưởng</t>
   </si>
   <si>
     <t xml:space="preserve">1. Hoạt động bắt đầu sau, ngài mỗi ngày nhưng khiêu chiến  Một chương . Mỗi một chương chia làm ba tiểu quan, nhất định phải theo thứ tự khiêu chiến mỗi một quan.&lt;br&gt;2. Ngài có thể sử dụng  Dự thiết tướng , tự do phối hợp người chậm tiến đi chiến đấu. Chiến đấu như có  Tất bên trên tướng , thì đại biểu chiến đấu bên trong nhất định phải sử dụng nên tướng ra trận, không sử dụng nên tướng đem  Không cách nào bắt đầu chiến đấu .</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">1. Mỗi thông qua một chương có thể nhận đối ứng thưởng, cũng có thể trả tiền mua ngoài định mức gói quà.&lt;br&gt;2. Nếu như chưa thông qua đối ứng chương tiết, không cách nào nhận hoặc mua.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Hoạt động trong lúc đó nhận được  Tướng điểm tích lũy  Càng nhiều, có thể nhận thưởng càng phong phú,  Tướng điểm tích lũy  Có thể thông qua hoàn thành nhiệm vụ nhận được.&lt;br&gt;2. Tướng điểm tích lũy  Đồng dạng có thể thông qua tốn hao  Nguyên bảo  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa tướng chiến lệnh tiến giai thưởng, càng có  Nguyên bảo  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
+    <t xml:space="preserve">1. Hoạt động trong lúc đó nhận được  Tướng điểm tích lũy  Càng nhiều, có thể nhận thưởng càng phong phú,  Tướng điểm tích lũy  Có thể thông qua hoàn thành nhiệm vụ nhận được.&lt;br&gt;2. Tướng điểm tích lũy  Đồng dạng có thể thông qua tốn hao  Kim cương  Phương thức hối đoái.&lt;br&gt;4. Trả tiền giải tỏa tướng chiến lệnh tiến giai thưởng, càng có  Kim cương  Cùng hi hữu vật liệu trực tiếp đưa.&lt;br&gt;5. Hoạt động kết thúc sau, tích lũy cấp, nhiệm vụ tiến độ cùng kinh nghiệm đều đem bị thanh không, đã kích hoạt chưa nhận thưởng sẽ thông qua bưu kiện cấp cho, mời kịp thời hoàn thành nhiệm vụ, nhận tương ứng thưởng, để tránh bỏ lỡ thưởng a!</t>
   </si>
   <si>
     <t xml:space="preserve">Thần trang tiến giai</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">Thượng cổ chi chiến cửa vào</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Hoạt động trong lúc đó phúc bé con thăng cấp cấp giữ lại, hoạt động trong lúc đó sẽ không tiến đi thiết lập lại. Phúc bé con cấp tối cao vì 300 Cấp, 150 Cấp về sau đem Mạnh bà tiến giai thành năm con cọp phúc bé con &lt;br&gt;2. Hoạt động trong lúc đó đánh bại các loại ma quái năm thú có thể lấy được lấy tinh phách giá trị, tinh phách giá trị nhưng tại tinh phách hối đoái bên trong hối đoái xa hoa quà tặng, phẩm chất tương đối cao niên kỉ thú có xác suất rơi xuống  Trứng rồng xác  Chờ đạo cụ &lt;br&gt;3. Sử dụng Nguyên bảo hoặc là  Phúc bé con lên thẳng khoán  Thăng cấp phúc bé con có thể tăng lên đánh giết ma quái năm thú hiệu suất &lt;br&gt;4. Mỗi ngày nhưng tại khu ma treo thưởng đăng nhập nhiệm vụ bên trong nhận 10 Trương  Năm thú lệnh truy nã , hoàn thành các loại khu ma treo thưởng bên trong nhiệm vụ, có thể lấy được lấy các loại hoạt động quà tặng cùng Nguyên bảo, mỗi ngày hoàn thành 10 Cái nhiệm vụ, còn có thể ngoài định mức một phần  Phúc bé con bánh kẹo bao &lt;br&gt;5. Đánh giết màu đỏ độ khó niên kỉ thú, trừ thu hoạch tinh phách giá trị bên ngoài, còn có thể nhận được  Tiên Khí tinh hoa .&lt;br&gt;6. Đánh giết năm thú số lượng đem bị thống kê tiến vào hồng nhân bảng, tại hoạt động kết thúc về sau, nhận được xếp hạng người chơi có thể lấy được lấy hạn định xưng hào.&lt;br&gt;7. Khiêu chiến ma quái năm thú cần tiêu hao khác biệt số lượng  Năm thú lệnh truy nã , lục sắc phẩm chất 1 Trương; Màu lam phẩm chất 2 Trương; Tử sắc phẩm chất 4 Trương; Màu cam phẩm chất 5 Trương, màu đỏ phẩm chất 6 Trương.</t>
+    <t xml:space="preserve">1. Hoạt động trong lúc đó phúc bé con thăng cấp cấp giữ lại, hoạt động trong lúc đó sẽ không tiến đi thiết lập lại. Phúc bé con cấp tối cao vì 300 Cấp, 150 Cấp về sau đem Mạnh bà tiến giai thành năm con cọp phúc bé con &lt;br&gt;2. Hoạt động trong lúc đó đánh bại các loại ma quái năm thú có thể lấy được lấy tinh phách giá trị, tinh phách giá trị nhưng tại tinh phách hối đoái bên trong hối đoái xa hoa quà tặng, phẩm chất tương đối cao niên kỉ thú có xác suất rơi xuống  Trứng rồng xác  Chờ đạo cụ &lt;br&gt;3. Sử dụng Kim cương hoặc là  Phúc bé con lên thẳng khoán  Thăng cấp phúc bé con có thể tăng lên đánh giết ma quái năm thú hiệu suất &lt;br&gt;4. Mỗi ngày nhưng tại khu ma treo thưởng đăng nhập nhiệm vụ bên trong nhận 10 Trương  Năm thú lệnh truy nã , hoàn thành các loại khu ma treo thưởng bên trong nhiệm vụ, có thể lấy được lấy các loại hoạt động quà tặng cùng Kim cương, mỗi ngày hoàn thành 10 Cái nhiệm vụ, còn có thể ngoài định mức một phần  Phúc bé con bánh kẹo bao &lt;br&gt;5. Đánh giết màu đỏ độ khó niên kỉ thú, trừ thu hoạch tinh phách giá trị bên ngoài, còn có thể nhận được  Tiên Khí tinh hoa .&lt;br&gt;6. Đánh giết năm thú số lượng đem bị thống kê tiến vào hồng nhân bảng, tại hoạt động kết thúc về sau, nhận được xếp hạng người chơi có thể lấy được lấy hạn định xưng hào.&lt;br&gt;7. Khiêu chiến ma quái năm thú cần tiêu hao khác biệt số lượng  Năm thú lệnh truy nã , lục sắc phẩm chất 1 Trương; Màu lam phẩm chất 2 Trương; Tử sắc phẩm chất 4 Trương; Màu cam phẩm chất 5 Trương, màu đỏ phẩm chất 6 Trương.</t>
   </si>
   <si>
     <t xml:space="preserve">Thượng cổ chi run run trận</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">Lục giới Thánh Điện</t>
   </si>
   <si>
-    <t xml:space="preserve">1, mỗi ngày có 1 Lần miễn phí càn quét lượt; Nhưng tốn hao Nguyên bảo ngoài định mức mua càn quét lượt. Càn quét lúc, sẽ căn cứ trước mắt lựa chọn độ khó cửa ải nhận được thưởng &lt;br&gt;2, cửa ải khiêu chiến lúc, có thể thông qua tướng tướng lân cận hai tướng kết nối hợp thành càng lớn càng cao cấp tướng tiến hành khiêu chiến. Tướng kết nối số lượng càng nhiều hợp thành tướng cấp càng cao, chiến lực càng cao &lt;br&gt;3, cửa ải mỗi tuần thiết lập lại một lần, có thể một lần nữa khiêu chiến a</t>
+    <t xml:space="preserve">1, mỗi ngày có 1 Lần miễn phí càn quét lượt; Nhưng tốn hao Kim cương ngoài định mức mua càn quét lượt. Càn quét lúc, sẽ căn cứ trước mắt lựa chọn độ khó cửa ải nhận được thưởng &lt;br&gt;2, cửa ải khiêu chiến lúc, có thể thông qua tướng tướng lân cận hai tướng kết nối hợp thành càng lớn càng cao cấp tướng tiến hành khiêu chiến. Tướng kết nối số lượng càng nhiều hợp thành tướng cấp càng cao, chiến lực càng cao &lt;br&gt;3, cửa ải mỗi tuần thiết lập lại một lần, có thể một lần nữa khiêu chiến a</t>
   </si>
   <si>
     <t xml:space="preserve">Cạnh đoán nói rõ</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Chủng tộc thi đấu chung  3 Cái giai đoạn:  Báo danh (1 Trời ),  Thi dự tuyển (1 Trời ),  Đấu vòng loại (1 Trời )&lt;br&gt;2. Mỗi lần hoạt động chỉ có thể hạn định đơn nhất chủng tộc tướng ra trận. Mỗi cái chủng tộc lịch đấu tiếp tục  3 Trời, tranh tài thời gian phân biệt là tuần  1-3, tuần  4-6, chủ nhật luân không.3 Thứ hai vòng.&lt;br&gt;3. Báo danh lúc, người chơi cần phân biệt phái ra 1V1,2V2,3V3 Ba cái đội hình, ba trận đối chiến ra trận tướng không thể lặp lại, một khi báo danh sau, đem không cách nào thay đổi dự thi tướng, chỉ có thể tại cái này 6 Tướng ở giữa điều chỉnh.&lt;br&gt;4. Thi dự tuyển bắt đầu sau, sẽ tiến hành 9 Vòng xứng đôi thi đấu, căn cứ thắng bại tuyển ra 64 Tên mạnh nhất người chơi.&lt;br&gt;4. Đấu loại kết thúc sau, sẽ căn cứ người chơi đấu loại điểm tích lũy chuyển đổi thành đối ứng thải sắc vỏ sò, thải sắc vỏ sò có thể dùng tại chủng tộc thi đấu cửa hàng hối đoái đạo cụ.&lt;br&gt;5. Đấu vòng loại sẽ đem 64 Mạnh ngẫu nhiên Xáo trộn  Xứng đôi tiến hành đấu vòng loại, cuối cùng quyết ra quán quân &lt;br&gt;6. Người chơi tại đấu vòng loại bắt đầu trước, có thể đối 64 Vị đấu vòng loại người chơi tiến hành cạnh đoán, đoán đúng có thể đạt được Nguyên bảo thưởng.</t>
+    <t xml:space="preserve">1. Chủng tộc thi đấu chung  3 Cái giai đoạn:  Báo danh (1 Trời ),  Thi dự tuyển (1 Trời ),  Đấu vòng loại (1 Trời )&lt;br&gt;2. Mỗi lần hoạt động chỉ có thể hạn định đơn nhất chủng tộc tướng ra trận. Mỗi cái chủng tộc lịch đấu tiếp tục  3 Trời, tranh tài thời gian phân biệt là tuần  1-3, tuần  4-6, chủ nhật luân không.3 Thứ hai vòng.&lt;br&gt;3. Báo danh lúc, người chơi cần phân biệt phái ra 1V1,2V2,3V3 Ba cái đội hình, ba trận đối chiến ra trận tướng không thể lặp lại, một khi báo danh sau, đem không cách nào thay đổi dự thi tướng, chỉ có thể tại cái này 6 Tướng ở giữa điều chỉnh.&lt;br&gt;4. Thi dự tuyển bắt đầu sau, sẽ tiến hành 9 Vòng xứng đôi thi đấu, căn cứ thắng bại tuyển ra 64 Tên mạnh nhất người chơi.&lt;br&gt;4. Đấu loại kết thúc sau, sẽ căn cứ người chơi đấu loại điểm tích lũy chuyển đổi thành đối ứng thải sắc vỏ sò, thải sắc vỏ sò có thể dùng tại chủng tộc thi đấu cửa hàng hối đoái đạo cụ.&lt;br&gt;5. Đấu vòng loại sẽ đem 64 Mạnh ngẫu nhiên Xáo trộn  Xứng đôi tiến hành đấu vòng loại, cuối cùng quyết ra quán quân &lt;br&gt;6. Người chơi tại đấu vòng loại bắt đầu trước, có thể đối 64 Vị đấu vòng loại người chơi tiến hành cạnh đoán, đoán đúng có thể đạt được Kim cương thưởng.</t>
   </si>
   <si>
     <t xml:space="preserve">Cảnh giới nói rõ</t>

--- a/server/excel/release/system-text.xlsx
+++ b/server/excel/release/system-text.xlsx
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">Mê cung chiến lệnh - Nữ Oa thạch</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Chiến sĩ, pháp sư, xe tăng, phụ trợ  4 Cái nghề nghiệp đối ứng  4 Trương khác biệt tinh tú đồ, mỗi một trương tinh tú bản vẽ chỉ đối ứng nghề nghiệp tăng thêm.&lt;br&gt;2. Mỗi một trương tinh tú đồ hạ đều có  7 Khỏa khác biệt tinh tú, mỗi một khỏa tinh tú cấp hạn mức cao nhất vì  10 Cấp, mỗi một khỏa tinh tú thăng cấp đến max cấp sau tự động mở ra tiếp theo khỏa tinh tú (10 Cấp đầy tinh ).&lt;br&gt;3. Người chơi tướng tinh túc mỗi cái cấp tinh tinh toàn bộ thắp sáng, tự động mở ra này tinh tú tiếp theo cấp.</t>
+    <t xml:space="preserve">1. Chiến sĩ, pháp sư, xe tăng, phụ trợ  4 Cái nghề nghiệp đối ứng  4 Trương khác biệt tinh tú đồ, mỗi một trương tinh tú bản vẽ chỉ đối ứng nghề nghiệp tăng thêm.&lt;br&gt;2. Mỗi một trương tinh tú đồ hạ đều có  7 Khỏa khác biệt tinh tú, mỗi một khỏa tinh tú cấp tối đa vì  10 Cấp, mỗi một khỏa tinh tú thăng cấp đến max cấp sau tự động mở ra tiếp theo khỏa tinh tú (10 Cấp đầy tinh ).&lt;br&gt;3. Người chơi tướng tinh túc mỗi cái cấp tinh tinh toàn bộ thắp sáng, tự động mở ra này tinh tú tiếp theo cấp.</t>
   </si>
   <si>
     <t xml:space="preserve">Mê cung chiến lệnh - Tinh tú đồ</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">Tỉ ấn đột phá</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Chân Long ấn cường hóa cấp hạn mức cao nhất là  15 Cấp, người chơi mỗi cường hóa thăng cấp  1 Lần tỉ ấn, đều đem tăng lên Chân Long ấn thuộc tính cơ sở ( Công kích, sinh mệnh, tốc độ hoặc phòng ngự ).&lt;br&gt;2. Chân Long ấn cường hóa cấp đến chỉ định lượt sau, nhất định  1 Đầu ngoài định mức tiến giai thuộc tính cũng tăng lên  1 Đầu tỉ ấn kỹ năng cấp.&lt;br&gt;3. Chân Long ấn thăng cấp lúc, như tỉ ấn kỹ năng cấp bậc là trung cấp cùng cao cấp lúc, ưu tiên thăng cấp trung cấp kỹ năng; Như hai cái tỉ ấn kỹ năng cấp đều vì cao cấp lúc, ưu tiên thăng cấp cái thứ nhất tỉ ấn kỹ năng &lt;br&gt;4. Chân Long ấn cường hóa đến max cấp chắc chắn tỉ ấn kỹ năng cấp tăng lên tới max cấp.&lt;br&gt;5. Chân Long ấn chưa cường hóa đến max cấp trước, tỉ ấn tiến giai thuộc tính không thể tiến hành đúc lại.&lt;br&gt;6. Tỉ ấn thuộc tính cơ sở cùng tỉ ấn kỹ năng tại chưa đầy cấp trước có thể tiến hành đúc lại.</t>
+    <t xml:space="preserve">1. Chân Long ấn cường hóa cấp tối đa là  15 Cấp, người chơi mỗi cường hóa thăng cấp  1 Lần tỉ ấn, đều đem tăng lên Chân Long ấn thuộc tính cơ sở ( Công kích, sinh mệnh, tốc độ hoặc phòng ngự ).&lt;br&gt;2. Chân Long ấn cường hóa cấp đến chỉ định lượt sau, nhất định  1 Đầu ngoài định mức tiến giai thuộc tính cũng tăng lên  1 Đầu tỉ ấn kỹ năng cấp.&lt;br&gt;3. Chân Long ấn thăng cấp lúc, như tỉ ấn kỹ năng cấp bậc là trung cấp cùng cao cấp lúc, ưu tiên thăng cấp trung cấp kỹ năng; Như hai cái tỉ ấn kỹ năng cấp đều vì cao cấp lúc, ưu tiên thăng cấp cái thứ nhất tỉ ấn kỹ năng &lt;br&gt;4. Chân Long ấn cường hóa đến max cấp chắc chắn tỉ ấn kỹ năng cấp tăng lên tới max cấp.&lt;br&gt;5. Chân Long ấn chưa cường hóa đến max cấp trước, tỉ ấn tiến giai thuộc tính không thể tiến hành đúc lại.&lt;br&gt;6. Tỉ ấn thuộc tính cơ sở cùng tỉ ấn kỹ năng tại chưa đầy cấp trước có thể tiến hành đúc lại.</t>
   </si>
   <si>
     <t xml:space="preserve">Tỉ ấn cường hóa</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">Tướng trùng sinh</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tướng thăng đến  10 Tinh lúc mở ra phó tướng hệ thống, cũng đồng bộ giải tỏa thứ  1 Cái phó tướng cột vị,  11 Tinh lúc giải tỏa thứ  2 Cái phó tướng cột vị,  13 Tinh lúc giải tỏa thứ  3 Cái phó tướng cột vị.&lt;br&gt;2. Phó tướng cột vị cùng chia hai loại: Chủng tộc phó tướng cột vị, chuyên môn phó tướng cột vị. Chủng tộc phó tướng cột vị cần cất đặt chỉ định chủng tộc tướng mới có thể kích hoạt thuộc tính; Chuyên môn phó tướng cột vị cần cất đặt đặc biệt tướng mới có thể kích hoạt thuộc tính.&lt;br&gt;3. Để vào phó tướng cột vị tướng Tinh cấp càng cao; Tăng thêm thuộc tính cũng càng cao &lt;br&gt;4. Phó tướng cột vị chỉ có thể để vào  5-14 Tinh tướng.&lt;br&gt;5. Phó tướng cột vị Tinh cấp hạn mức cao nhất cùng  Tướng bản thể Tinh cấp  Tương quan, để vào cột vị phó tướng Tinh cấp không thể vượt qua tướng bản thể Tinh cấp.&lt;br&gt;6. Tướng bị để vào phó tướng cột vị sau, không thể lại tiến hành cái khác thao tác, dỡ xuống sau mới có thể khôi phục bình thường sử dụng.</t>
+    <t xml:space="preserve">1. Tướng thăng đến  10 Tinh lúc mở ra phó tướng hệ thống, cũng đồng bộ giải tỏa thứ  1 Cái phó tướng cột vị,  11 Tinh lúc giải tỏa thứ  2 Cái phó tướng cột vị,  13 Tinh lúc giải tỏa thứ  3 Cái phó tướng cột vị.&lt;br&gt;2. Phó tướng cột vị cùng chia hai loại: Chủng tộc phó tướng cột vị, chuyên môn phó tướng cột vị. Chủng tộc phó tướng cột vị cần cất đặt chỉ định chủng tộc tướng mới có thể kích hoạt thuộc tính; Chuyên môn phó tướng cột vị cần cất đặt đặc biệt tướng mới có thể kích hoạt thuộc tính.&lt;br&gt;3. Để vào phó tướng cột vị tướng Tinh cấp càng cao; Tăng thêm thuộc tính cũng càng cao &lt;br&gt;4. Phó tướng cột vị chỉ có thể để vào  5-14 Tinh tướng.&lt;br&gt;5. Phó tướng cột vị Tinh cấp tối đa cùng  Tướng bản thể Tinh cấp  Tương quan, để vào cột vị phó tướng Tinh cấp không thể vượt qua tướng bản thể Tinh cấp.&lt;br&gt;6. Tướng bị để vào phó tướng cột vị sau, không thể lại tiến hành cái khác thao tác, dỡ xuống sau mới có thể khôi phục bình thường sử dụng.</t>
   </si>
   <si>
     <t xml:space="preserve">Tướng phó tướng</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">Trân tàng bảo hạp</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Có được 1 Cái đã tiến giai thú hồn liền có thể mở ra nên loại thú hồn cộng minh giao diện &lt;br&gt;2. Tiến giai qua đồng loại thú hồn bên trong cấp tối cao thú hồn sẽ tự động trở thành cộng minh chủ thể, cấp đem làm cộng minh thủy tinh cấp &lt;br&gt;3. Cộng minh cột vị bên trong có thể để vào đã tiến giai đồng loại thú hồn, để vào sau cấp đem tự động tăng lên đến cộng minh thủy tinh cấp, nhưng tăng lên cấp hạn mức cao nhất thụ thú hồn cấp số ảnh hưởng.&lt;br&gt;4. Đã tiến giai thú hồn để vào cột vị sau, thú này hồn thì không thể thăng cấp, không thể cản làm thôn phệ cùng tiến giai vật liệu, nhưng có thể bình thường sử dụng cùng thú hồn tẩy luyện &lt;br&gt;5. Cột vị mở ra cần tiêu hao  Cộng minh thủy tinh &lt;br&gt;6. Đương thú hồn rời đi cột vị lúc, cột vị sẽ tiến vào  24 Giờ thời gian cooldown, có thể tốn hao Kim cương đổi mới thời gian cooldown</t>
+    <t xml:space="preserve">1. Có được 1 Cái đã tiến giai thú hồn liền có thể mở ra nên loại thú hồn cộng minh giao diện &lt;br&gt;2. Tiến giai qua đồng loại thú hồn bên trong cấp tối cao thú hồn sẽ tự động trở thành cộng minh chủ thể, cấp đem làm cộng minh thủy tinh cấp &lt;br&gt;3. Cộng minh cột vị bên trong có thể để vào đã tiến giai đồng loại thú hồn, để vào sau cấp đem tự động tăng lên đến cộng minh thủy tinh cấp, nhưng tăng lên cấp tối đa thụ thú hồn cấp số ảnh hưởng.&lt;br&gt;4. Đã tiến giai thú hồn để vào cột vị sau, thú này hồn thì không thể thăng cấp, không thể cản làm thôn phệ cùng tiến giai vật liệu, nhưng có thể bình thường sử dụng cùng thú hồn tẩy luyện &lt;br&gt;5. Cột vị mở ra cần tiêu hao  Cộng minh thủy tinh &lt;br&gt;6. Đương thú hồn rời đi cột vị lúc, cột vị sẽ tiến vào  24 Giờ thời gian cooldown, có thể tốn hao Kim cương đổi mới thời gian cooldown</t>
   </si>
   <si>
     <t xml:space="preserve">Điển tàng bảo hạp</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">Vượt phục PVP- Chủ bảng</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Phong Thần đài mở ra sau tự động lựa chọn năm cấp bậc tối cao tướng làm cung phụng tướng, năm trong đó  Cấp thấp nhất  Làm Phong Thần đài cấp &lt;br&gt;2. Để vào phía dưới cột vị bên trong tướng cấp tự động tăng lên đến Phong Thần đài cấp, cấp số cũng tự động tăng lên đến cùng cung phụng tướng bên trong cấp thấp nhất tướng giống nhau, cũng kích hoạt đối ứng kỹ năng cùng thuộc tính tăng thêm. Sau khi tăng lên tướng cấp cùng cấp số vẫn nhận tướng phẩm chất hạn chế &lt;br&gt;3. Để vào phía dưới cột vị tướng có thể thăng tinh, nhưng là cấm chỉ thăng cấp, cấm chỉ làm thăng tinh vật liệu, không cách nào tiến hành dung hợp, hiến tế, lui trở về chờ thao tác &lt;br&gt;4. Đương cột vị bên trong tướng rời đi sau, cột vị sẽ tiến vào 24 Giờ làm lạnh, làm lạnh hoàn tất sau mới có thể để vào mới tướng &lt;br&gt;5. Người chơi nhưng tiêu hao anh linh mảnh đổi mới cột vị thời gian cooldown, anh linh mảnh tại thông quan 50 Cấp lịch luyện sau nhưng treo máy nhận được &lt;br&gt;6. Đương năm cái cho phụng tướng đều đến 340 Cấp, cái này năm tướng đem hoàn nguyên đến 1 Cấp, cũng tự động để vào Phong Thần đài tướng cột bên trong ( Hệ thống đưa tặng năm tướng cột vị ), năm vị cung phụng tướng thăng cấp tài nguyên sẽ không trả về, từ đó đổi lấy Phong Thần đài đột phá 340 Cấp cấp hạn mức cao nhất &lt;br&gt;7. Phong Thần đài đột phá 340 Cấp hạn mức cao nhất sau, sẽ không còn ỷ lại cung phụng tướng tăng lên cấp. Nhưng tiêu hao tài nguyên đem Phong Thần đài cấp, cột vị bên trong tướng đem tùy theo đồng bộ tăng lên cấp &lt;br&gt;8. Phong Thần đài cấp hạn mức cao nhất từ người chơi bồi dưỡng được  12/13/14 Tinh nhân vật số lượng quyết định, mỗi một cái  12/13/14 Tinh nhân vật, vì Phong Thần đài gia tăng  2/4/6 Cấp hạn mức cao nhất &lt;br&gt;9. Tướng cột vị nhưng tiêu hao  Anh linh mảnh  Hoặc  Kim cương  Mở rộng, anh linh mảnh tại lịch luyện chủ tuyến treo máy bên trong nhận được</t>
+    <t xml:space="preserve">1. Phong Thần đài mở ra sau tự động lựa chọn năm cấp bậc tối cao tướng làm cung phụng tướng, năm trong đó  Cấp thấp nhất  Làm Phong Thần đài cấp &lt;br&gt;2. Để vào phía dưới cột vị bên trong tướng cấp tự động tăng lên đến Phong Thần đài cấp, cấp số cũng tự động tăng lên đến cùng cung phụng tướng bên trong cấp thấp nhất tướng giống nhau, cũng kích hoạt đối ứng kỹ năng cùng thuộc tính tăng thêm. Sau khi tăng lên tướng cấp cùng cấp số vẫn nhận tướng phẩm chất hạn chế &lt;br&gt;3. Để vào phía dưới cột vị tướng có thể thăng tinh, nhưng là cấm chỉ thăng cấp, cấm chỉ làm thăng tinh vật liệu, không cách nào tiến hành dung hợp, hiến tế, lui trở về chờ thao tác &lt;br&gt;4. Đương cột vị bên trong tướng rời đi sau, cột vị sẽ tiến vào 24 Giờ làm lạnh, làm lạnh hoàn tất sau mới có thể để vào mới tướng &lt;br&gt;5. Người chơi nhưng tiêu hao anh linh mảnh đổi mới cột vị thời gian cooldown, anh linh mảnh tại thông quan 50 Cấp lịch luyện sau nhưng treo máy nhận được &lt;br&gt;6. Đương năm cái cho phụng tướng đều đến 340 Cấp, cái này năm tướng đem hoàn nguyên đến 1 Cấp, cũng tự động để vào Phong Thần đài tướng cột bên trong ( Hệ thống đưa tặng năm tướng cột vị ), năm vị cung phụng tướng thăng cấp tài nguyên sẽ không trả về, từ đó đổi lấy Phong Thần đài đột phá 340 Cấp cấp tối đa &lt;br&gt;7. Phong Thần đài đột phá 340 Cấp tối đa sau, sẽ không còn ỷ lại cung phụng tướng tăng lên cấp. Nhưng tiêu hao tài nguyên đem Phong Thần đài cấp, cột vị bên trong tướng đem tùy theo đồng bộ tăng lên cấp &lt;br&gt;8. Phong Thần đài cấp tối đa từ người chơi bồi dưỡng được  12/13/14 Tinh nhân vật số lượng quyết định, mỗi một cái  12/13/14 Tinh nhân vật, vì Phong Thần đài gia tăng  2/4/6 Cấp tối đa &lt;br&gt;9. Tướng cột vị nhưng tiêu hao  Anh linh mảnh  Hoặc  Kim cương  Mở rộng, anh linh mảnh tại lịch luyện chủ tuyến treo máy bên trong nhận được</t>
   </si>
   <si>
     <t xml:space="preserve">1. Mỗi  Thứ sáu 20 Điểm đến  Thứ bảy 20 Điểm có thể đối vượt phục PVP32 Cường đội ngũ tiến hành  Quan ,  Á ,  Quý  Quân cạnh đoán.&lt;br&gt;2. Cạnh đoán cần tốn hao nhất định Kim cương, đoán đúng nhưng  Gấp bội  Trả về, đoán sai đem  Toàn bộ khấu trừ .&lt;br&gt;3. Chỉ có thể đối trong đó  1 Chi đội ngũ cạnh đoán  1 Loại thứ tự.&lt;br&gt;4. Chỉ có thể ở cạnh đoán trong lúc đó tiến hành cạnh đoán.&lt;br&gt;5. Cuối cùng thưởng sẽ tại đấu vòng loại kết thúc sau từ  Bưu kiện  Cấp cho.</t>
